--- a/data/score_result.xlsx
+++ b/data/score_result.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="个人每场成绩" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="队伍总体情况" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="个人每场成绩" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="队伍总体情况" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH59"/>
+  <dimension ref="A1:AH60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>82.97</v>
+        <v>84.04000000000001</v>
       </c>
       <c r="E2" t="n">
         <v>10</v>
@@ -626,7 +626,7 @@
         <v>15</v>
       </c>
       <c r="G2" t="n">
-        <v>98.25</v>
+        <v>98.98999999999999</v>
       </c>
       <c r="H2" t="n">
         <v>8</v>
@@ -635,7 +635,7 @@
         <v>25</v>
       </c>
       <c r="J2" t="n">
-        <v>77.59999999999999</v>
+        <v>78.68000000000001</v>
       </c>
       <c r="K2" t="n">
         <v>8</v>
@@ -644,7 +644,7 @@
         <v>14</v>
       </c>
       <c r="M2" t="n">
-        <v>87.44</v>
+        <v>87.91</v>
       </c>
       <c r="N2" t="n">
         <v>9</v>
@@ -653,7 +653,7 @@
         <v>19</v>
       </c>
       <c r="P2" t="n">
-        <v>87.98</v>
+        <v>88.59</v>
       </c>
       <c r="Q2" t="n">
         <v>8</v>
@@ -662,7 +662,7 @@
         <v>29</v>
       </c>
       <c r="S2" t="n">
-        <v>77.2</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="T2" t="n">
         <v>7</v>
@@ -671,7 +671,7 @@
         <v>147</v>
       </c>
       <c r="V2" t="n">
-        <v>63.58</v>
+        <v>67.36</v>
       </c>
       <c r="W2" s="1" t="n">
         <v>5</v>
@@ -680,7 +680,7 @@
         <v>315</v>
       </c>
       <c r="Y2" s="1" t="n">
-        <v>27.61</v>
+        <v>31.76</v>
       </c>
       <c r="Z2" s="1" t="n">
         <v>5</v>
@@ -689,7 +689,7 @@
         <v>112</v>
       </c>
       <c r="AB2" s="1" t="n">
-        <v>53.83</v>
+        <v>55.37</v>
       </c>
       <c r="AC2" s="1" t="n">
         <v>0</v>
@@ -707,7 +707,7 @@
         <v>12</v>
       </c>
       <c r="AH2" t="n">
-        <v>88.76000000000001</v>
+        <v>88.70999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -725,16 +725,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>77.06</v>
-      </c>
-      <c r="E3" s="1" t="n">
+        <v>77.54000000000001</v>
+      </c>
+      <c r="E3" t="n">
         <v>6</v>
       </c>
-      <c r="F3" s="1" t="n">
+      <c r="F3" t="n">
         <v>103</v>
       </c>
-      <c r="G3" s="1" t="n">
-        <v>52.35</v>
+      <c r="G3" t="n">
+        <v>55.58</v>
       </c>
       <c r="H3" t="n">
         <v>9</v>
@@ -743,7 +743,7 @@
         <v>16</v>
       </c>
       <c r="J3" t="n">
-        <v>88.31</v>
+        <v>89.06999999999999</v>
       </c>
       <c r="K3" t="n">
         <v>8</v>
@@ -752,7 +752,7 @@
         <v>17</v>
       </c>
       <c r="M3" t="n">
-        <v>87.11</v>
+        <v>87.69</v>
       </c>
       <c r="N3" t="n">
         <v>7</v>
@@ -761,7 +761,7 @@
         <v>45</v>
       </c>
       <c r="P3" t="n">
-        <v>66.15000000000001</v>
+        <v>67.31</v>
       </c>
       <c r="Q3" t="n">
         <v>9</v>
@@ -770,7 +770,7 @@
         <v>14</v>
       </c>
       <c r="S3" t="n">
-        <v>88.54000000000001</v>
+        <v>88.98</v>
       </c>
       <c r="T3" t="n">
         <v>7</v>
@@ -779,7 +779,7 @@
         <v>21</v>
       </c>
       <c r="V3" t="n">
-        <v>75.83</v>
+        <v>76.34999999999999</v>
       </c>
       <c r="W3" s="1" t="n">
         <v>0</v>
@@ -799,14 +799,14 @@
       <c r="AB3" s="1" t="n">
         <v>-0</v>
       </c>
-      <c r="AC3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD3" t="n">
+      <c r="AC3" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD3" s="1" t="n">
         <v>90</v>
       </c>
-      <c r="AE3" t="n">
-        <v>55.55</v>
+      <c r="AE3" s="1" t="n">
+        <v>55.41</v>
       </c>
       <c r="AF3" t="n">
         <v>8</v>
@@ -815,7 +815,7 @@
         <v>22</v>
       </c>
       <c r="AH3" t="n">
-        <v>77.90000000000001</v>
+        <v>77.81</v>
       </c>
     </row>
     <row r="4">
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>76.12</v>
+        <v>76.97</v>
       </c>
       <c r="E4" t="n">
         <v>9</v>
@@ -842,25 +842,25 @@
         <v>27</v>
       </c>
       <c r="G4" t="n">
-        <v>87.08</v>
-      </c>
-      <c r="H4" s="1" t="n">
+        <v>88.31</v>
+      </c>
+      <c r="H4" t="n">
         <v>7</v>
       </c>
-      <c r="I4" s="1" t="n">
+      <c r="I4" t="n">
         <v>129</v>
       </c>
-      <c r="J4" s="1" t="n">
-        <v>58.8</v>
-      </c>
-      <c r="K4" t="n">
+      <c r="J4" t="n">
+        <v>63.85</v>
+      </c>
+      <c r="K4" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4" s="1" t="n">
         <v>69</v>
       </c>
-      <c r="M4" t="n">
-        <v>61</v>
+      <c r="M4" s="1" t="n">
+        <v>62.84</v>
       </c>
       <c r="N4" s="1" t="n">
         <v>5</v>
@@ -869,7 +869,7 @@
         <v>144</v>
       </c>
       <c r="P4" s="1" t="n">
-        <v>41.06</v>
+        <v>43.76</v>
       </c>
       <c r="Q4" t="n">
         <v>7</v>
@@ -878,7 +878,7 @@
         <v>51</v>
       </c>
       <c r="S4" t="n">
-        <v>65.62</v>
+        <v>66.94</v>
       </c>
       <c r="T4" t="n">
         <v>8</v>
@@ -887,7 +887,7 @@
         <v>8</v>
       </c>
       <c r="V4" t="n">
-        <v>88.11</v>
+        <v>88.31999999999999</v>
       </c>
       <c r="W4" t="n">
         <v>9</v>
@@ -896,7 +896,7 @@
         <v>20</v>
       </c>
       <c r="Y4" t="n">
-        <v>79.88</v>
+        <v>80.33</v>
       </c>
       <c r="Z4" s="1" t="n">
         <v>4</v>
@@ -905,7 +905,7 @@
         <v>159</v>
       </c>
       <c r="AB4" s="1" t="n">
-        <v>40.12</v>
+        <v>41.88</v>
       </c>
       <c r="AC4" t="n">
         <v>6</v>
@@ -914,7 +914,7 @@
         <v>27</v>
       </c>
       <c r="AE4" t="n">
-        <v>72.56</v>
+        <v>72.52</v>
       </c>
       <c r="AF4" t="n">
         <v>8</v>
@@ -923,7 +923,7 @@
         <v>15</v>
       </c>
       <c r="AH4" t="n">
-        <v>78.59999999999999</v>
+        <v>78.54000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>71.36</v>
+        <v>72.72</v>
       </c>
       <c r="E5" t="n">
         <v>7</v>
@@ -950,7 +950,7 @@
         <v>76</v>
       </c>
       <c r="G5" t="n">
-        <v>63.44</v>
+        <v>66.20999999999999</v>
       </c>
       <c r="H5" t="n">
         <v>7</v>
@@ -959,7 +959,7 @@
         <v>65</v>
       </c>
       <c r="J5" t="n">
-        <v>64.40000000000001</v>
+        <v>66.92</v>
       </c>
       <c r="K5" t="n">
         <v>8</v>
@@ -968,7 +968,7 @@
         <v>26</v>
       </c>
       <c r="M5" t="n">
-        <v>86.11</v>
+        <v>87.01000000000001</v>
       </c>
       <c r="N5" s="1" t="n">
         <v>4</v>
@@ -977,7 +977,7 @@
         <v>264</v>
       </c>
       <c r="P5" s="1" t="n">
-        <v>26.85</v>
+        <v>30.82</v>
       </c>
       <c r="Q5" t="n">
         <v>7</v>
@@ -986,7 +986,7 @@
         <v>49</v>
       </c>
       <c r="S5" t="n">
-        <v>65.8</v>
+        <v>67.06</v>
       </c>
       <c r="T5" t="n">
         <v>7</v>
@@ -995,7 +995,7 @@
         <v>46</v>
       </c>
       <c r="V5" t="n">
-        <v>73.40000000000001</v>
+        <v>74.56999999999999</v>
       </c>
       <c r="W5" t="n">
         <v>8</v>
@@ -1004,7 +1004,7 @@
         <v>49</v>
       </c>
       <c r="Y5" t="n">
-        <v>68.36</v>
+        <v>69.38</v>
       </c>
       <c r="Z5" s="1" t="n">
         <v>5</v>
@@ -1013,7 +1013,7 @@
         <v>93</v>
       </c>
       <c r="AB5" s="1" t="n">
-        <v>55.31</v>
+        <v>56.59</v>
       </c>
       <c r="AC5" s="1" t="n">
         <v>0</v>
@@ -1031,7 +1031,7 @@
         <v>21</v>
       </c>
       <c r="AH5" t="n">
-        <v>78</v>
+        <v>77.91</v>
       </c>
     </row>
     <row r="6">
@@ -1049,7 +1049,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>70.92</v>
+        <v>71.98</v>
       </c>
       <c r="E6" t="n">
         <v>7</v>
@@ -1058,7 +1058,7 @@
         <v>56</v>
       </c>
       <c r="G6" t="n">
-        <v>65.19</v>
+        <v>67.22</v>
       </c>
       <c r="H6" t="n">
         <v>8</v>
@@ -1067,7 +1067,7 @@
         <v>36</v>
       </c>
       <c r="J6" t="n">
-        <v>76.5</v>
+        <v>78.08</v>
       </c>
       <c r="K6" t="n">
         <v>7</v>
@@ -1076,7 +1076,7 @@
         <v>30</v>
       </c>
       <c r="M6" t="n">
-        <v>74.95999999999999</v>
+        <v>75.87</v>
       </c>
       <c r="N6" t="n">
         <v>6</v>
@@ -1085,7 +1085,7 @@
         <v>68</v>
       </c>
       <c r="P6" t="n">
-        <v>54.97</v>
+        <v>56.49</v>
       </c>
       <c r="Q6" s="1" t="n">
         <v>6</v>
@@ -1094,7 +1094,7 @@
         <v>93</v>
       </c>
       <c r="S6" s="1" t="n">
-        <v>53.1</v>
+        <v>55.17</v>
       </c>
       <c r="T6" t="n">
         <v>8</v>
@@ -1103,7 +1103,7 @@
         <v>17</v>
       </c>
       <c r="V6" t="n">
-        <v>87.11</v>
+        <v>87.58</v>
       </c>
       <c r="W6" t="n">
         <v>7</v>
@@ -1112,7 +1112,7 @@
         <v>57</v>
       </c>
       <c r="Y6" t="n">
-        <v>59.18</v>
+        <v>60.22</v>
       </c>
       <c r="Z6" s="1" t="n">
         <v>10</v>
@@ -1139,7 +1139,7 @@
         <v>16</v>
       </c>
       <c r="AH6" t="n">
-        <v>78.5</v>
+        <v>78.43000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>66.70999999999999</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="E7" t="n">
         <v>7</v>
@@ -1166,7 +1166,7 @@
         <v>75</v>
       </c>
       <c r="G7" t="n">
-        <v>63.52</v>
+        <v>66.26000000000001</v>
       </c>
       <c r="H7" s="1" t="n">
         <v>6</v>
@@ -1175,7 +1175,7 @@
         <v>148</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>48.98</v>
+        <v>53.94</v>
       </c>
       <c r="K7" t="n">
         <v>7</v>
@@ -1184,7 +1184,7 @@
         <v>43</v>
       </c>
       <c r="M7" t="n">
-        <v>73.69</v>
+        <v>75.02</v>
       </c>
       <c r="N7" t="n">
         <v>7</v>
@@ -1193,7 +1193,7 @@
         <v>49</v>
       </c>
       <c r="P7" t="n">
-        <v>65.8</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="Q7" t="n">
         <v>7</v>
@@ -1202,7 +1202,7 @@
         <v>81</v>
       </c>
       <c r="S7" t="n">
-        <v>63</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="T7" t="n">
         <v>7</v>
@@ -1211,7 +1211,7 @@
         <v>127</v>
       </c>
       <c r="V7" t="n">
-        <v>65.53</v>
+        <v>68.79000000000001</v>
       </c>
       <c r="W7" s="1" t="n">
         <v>0</v>
@@ -1238,7 +1238,7 @@
         <v>75</v>
       </c>
       <c r="AE7" t="n">
-        <v>56.72</v>
+        <v>56.61</v>
       </c>
       <c r="AF7" t="n">
         <v>8</v>
@@ -1247,7 +1247,7 @@
         <v>14</v>
       </c>
       <c r="AH7" t="n">
-        <v>78.7</v>
+        <v>78.64</v>
       </c>
     </row>
     <row r="8">
@@ -1265,7 +1265,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>65.95999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="E8" t="n">
         <v>7</v>
@@ -1274,7 +1274,7 @@
         <v>61</v>
       </c>
       <c r="G8" t="n">
-        <v>64.75</v>
+        <v>66.97</v>
       </c>
       <c r="H8" t="n">
         <v>8</v>
@@ -1283,7 +1283,7 @@
         <v>51</v>
       </c>
       <c r="J8" t="n">
-        <v>75</v>
+        <v>77.25</v>
       </c>
       <c r="K8" t="n">
         <v>7</v>
@@ -1292,7 +1292,7 @@
         <v>50</v>
       </c>
       <c r="M8" t="n">
-        <v>73.01000000000001</v>
+        <v>74.56</v>
       </c>
       <c r="N8" t="n">
         <v>7</v>
@@ -1301,16 +1301,16 @@
         <v>54</v>
       </c>
       <c r="P8" t="n">
-        <v>65.36</v>
-      </c>
-      <c r="Q8" s="1" t="n">
+        <v>66.76000000000001</v>
+      </c>
+      <c r="Q8" t="n">
         <v>6</v>
       </c>
-      <c r="R8" s="1" t="n">
+      <c r="R8" t="n">
         <v>87</v>
       </c>
-      <c r="S8" s="1" t="n">
-        <v>53.55</v>
+      <c r="S8" t="n">
+        <v>55.48</v>
       </c>
       <c r="T8" t="n">
         <v>7</v>
@@ -1319,7 +1319,7 @@
         <v>145</v>
       </c>
       <c r="V8" t="n">
-        <v>63.78</v>
+        <v>67.5</v>
       </c>
       <c r="W8" s="1" t="n">
         <v>0</v>
@@ -1339,14 +1339,14 @@
       <c r="AB8" s="1" t="n">
         <v>-0</v>
       </c>
-      <c r="AC8" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD8" t="n">
+      <c r="AC8" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD8" s="1" t="n">
         <v>115</v>
       </c>
-      <c r="AE8" t="n">
-        <v>53.59</v>
+      <c r="AE8" s="1" t="n">
+        <v>53.42</v>
       </c>
       <c r="AF8" t="n">
         <v>7</v>
@@ -1355,7 +1355,7 @@
         <v>44</v>
       </c>
       <c r="AH8" t="n">
-        <v>66.23999999999999</v>
+        <v>66.06999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -1373,7 +1373,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>65.38</v>
+        <v>67.28</v>
       </c>
       <c r="E9" s="1" t="n">
         <v>5</v>
@@ -1382,7 +1382,7 @@
         <v>352</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>28.06</v>
+        <v>37.34</v>
       </c>
       <c r="H9" t="n">
         <v>7</v>
@@ -1391,7 +1391,7 @@
         <v>142</v>
       </c>
       <c r="J9" t="n">
-        <v>57.66</v>
+        <v>63.22</v>
       </c>
       <c r="K9" t="n">
         <v>6</v>
@@ -1400,7 +1400,7 @@
         <v>118</v>
       </c>
       <c r="M9" t="n">
-        <v>56.92</v>
+        <v>60.08</v>
       </c>
       <c r="N9" s="1" t="n">
         <v>5</v>
@@ -1409,7 +1409,7 @@
         <v>122</v>
       </c>
       <c r="P9" s="1" t="n">
-        <v>42.44</v>
+        <v>44.72</v>
       </c>
       <c r="Q9" s="1" t="n">
         <v>6</v>
@@ -1418,7 +1418,7 @@
         <v>207</v>
       </c>
       <c r="S9" s="1" t="n">
-        <v>44.55</v>
+        <v>49.18</v>
       </c>
       <c r="T9" t="n">
         <v>7</v>
@@ -1427,7 +1427,7 @@
         <v>93</v>
       </c>
       <c r="V9" t="n">
-        <v>68.83</v>
+        <v>71.20999999999999</v>
       </c>
       <c r="W9" t="n">
         <v>8</v>
@@ -1436,7 +1436,7 @@
         <v>43</v>
       </c>
       <c r="Y9" t="n">
-        <v>68.91</v>
+        <v>69.8</v>
       </c>
       <c r="Z9" t="n">
         <v>5</v>
@@ -1445,7 +1445,7 @@
         <v>111</v>
       </c>
       <c r="AB9" t="n">
-        <v>53.91</v>
+        <v>55.43</v>
       </c>
       <c r="AC9" t="n">
         <v>7</v>
@@ -1454,7 +1454,7 @@
         <v>17</v>
       </c>
       <c r="AE9" t="n">
-        <v>85.75</v>
+        <v>85.72</v>
       </c>
       <c r="AF9" t="n">
         <v>7</v>
@@ -1463,7 +1463,7 @@
         <v>50</v>
       </c>
       <c r="AH9" t="n">
-        <v>65.70999999999999</v>
+        <v>65.52</v>
       </c>
     </row>
     <row r="10">
@@ -1481,7 +1481,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>61.6</v>
+        <v>62.94</v>
       </c>
       <c r="E10" s="1" t="n">
         <v>0</v>
@@ -1501,14 +1501,14 @@
       <c r="J10" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="K10" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="L10" s="1" t="n">
+      <c r="K10" t="n">
+        <v>5</v>
+      </c>
+      <c r="L10" t="n">
         <v>174</v>
       </c>
-      <c r="M10" s="1" t="n">
-        <v>43.54</v>
+      <c r="M10" t="n">
+        <v>47.44</v>
       </c>
       <c r="N10" t="n">
         <v>7</v>
@@ -1517,7 +1517,7 @@
         <v>34</v>
       </c>
       <c r="P10" t="n">
-        <v>67.11</v>
+        <v>67.98</v>
       </c>
       <c r="Q10" t="n">
         <v>7</v>
@@ -1526,7 +1526,7 @@
         <v>75</v>
       </c>
       <c r="S10" t="n">
-        <v>63.52</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="T10" t="n">
         <v>7</v>
@@ -1535,16 +1535,16 @@
         <v>28</v>
       </c>
       <c r="V10" t="n">
-        <v>75.15000000000001</v>
-      </c>
-      <c r="W10" t="n">
+        <v>75.84999999999999</v>
+      </c>
+      <c r="W10" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="X10" t="n">
+      <c r="X10" s="1" t="n">
         <v>153</v>
       </c>
-      <c r="Y10" t="n">
-        <v>44.18</v>
+      <c r="Y10" s="1" t="n">
+        <v>46.59</v>
       </c>
       <c r="Z10" s="1" t="n">
         <v>3</v>
@@ -1553,7 +1553,7 @@
         <v>442</v>
       </c>
       <c r="AB10" s="1" t="n">
-        <v>16.83</v>
+        <v>20.5</v>
       </c>
       <c r="AC10" t="n">
         <v>5</v>
@@ -1562,7 +1562,7 @@
         <v>58</v>
       </c>
       <c r="AE10" t="n">
-        <v>58.05</v>
+        <v>57.96</v>
       </c>
       <c r="AF10" s="1" t="n">
         <v>5</v>
@@ -1571,7 +1571,7 @@
         <v>228</v>
       </c>
       <c r="AH10" s="1" t="n">
-        <v>35.81</v>
+        <v>35.18</v>
       </c>
     </row>
     <row r="11">
@@ -1589,7 +1589,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>56.53</v>
+        <v>58.53</v>
       </c>
       <c r="E11" t="n">
         <v>6</v>
@@ -1598,7 +1598,7 @@
         <v>181</v>
       </c>
       <c r="G11" t="n">
-        <v>46.5</v>
+        <v>52.21</v>
       </c>
       <c r="H11" s="1" t="n">
         <v>5</v>
@@ -1607,7 +1607,7 @@
         <v>476</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>20.31</v>
+        <v>33.69</v>
       </c>
       <c r="K11" t="n">
         <v>6</v>
@@ -1616,7 +1616,7 @@
         <v>93</v>
       </c>
       <c r="M11" t="n">
-        <v>59</v>
+        <v>61.49</v>
       </c>
       <c r="N11" t="n">
         <v>5</v>
@@ -1625,7 +1625,7 @@
         <v>220</v>
       </c>
       <c r="P11" t="n">
-        <v>36.31</v>
+        <v>40.45</v>
       </c>
       <c r="Q11" t="n">
         <v>8</v>
@@ -1634,7 +1634,7 @@
         <v>22</v>
       </c>
       <c r="S11" t="n">
-        <v>77.90000000000001</v>
+        <v>78.53</v>
       </c>
       <c r="T11" t="n">
         <v>7</v>
@@ -1643,7 +1643,7 @@
         <v>64</v>
       </c>
       <c r="V11" t="n">
-        <v>71.65000000000001</v>
+        <v>73.28</v>
       </c>
       <c r="W11" s="1" t="n">
         <v>0</v>
@@ -1670,7 +1670,7 @@
         <v>127</v>
       </c>
       <c r="AE11" t="n">
-        <v>52.66</v>
+        <v>52.47</v>
       </c>
       <c r="AF11" t="n">
         <v>6</v>
@@ -1679,7 +1679,7 @@
         <v>112</v>
       </c>
       <c r="AH11" t="n">
-        <v>51.67</v>
+        <v>51.31</v>
       </c>
     </row>
     <row r="12">
@@ -1688,106 +1688,106 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>team0976</t>
+          <t>team0994</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>蔡佩霖</t>
+          <t>吴显熠</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>54.02</v>
+        <v>56.44</v>
       </c>
       <c r="E12" t="n">
         <v>6</v>
       </c>
       <c r="F12" t="n">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="G12" t="n">
-        <v>47.32</v>
+        <v>52.81</v>
       </c>
       <c r="H12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I12" t="n">
-        <v>94</v>
+        <v>158</v>
       </c>
       <c r="J12" t="n">
-        <v>61.86</v>
+        <v>53.53</v>
       </c>
       <c r="K12" t="n">
         <v>6</v>
       </c>
       <c r="L12" t="n">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="M12" t="n">
-        <v>55.58</v>
-      </c>
-      <c r="N12" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="R12" s="1" t="n">
-        <v>932</v>
-      </c>
-      <c r="S12" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" s="1" t="n">
-        <v>1490</v>
-      </c>
-      <c r="V12" s="1" t="n">
-        <v>-0</v>
-      </c>
-      <c r="W12" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" s="1" t="n">
-        <v>1475</v>
-      </c>
-      <c r="Y12" s="1" t="n">
-        <v>-0</v>
+        <v>60.14</v>
+      </c>
+      <c r="N12" t="n">
+        <v>6</v>
+      </c>
+      <c r="O12" t="n">
+        <v>92</v>
+      </c>
+      <c r="P12" t="n">
+        <v>55.24</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>6</v>
+      </c>
+      <c r="R12" t="n">
+        <v>109</v>
+      </c>
+      <c r="S12" t="n">
+        <v>54.33</v>
+      </c>
+      <c r="T12" t="n">
+        <v>7</v>
+      </c>
+      <c r="U12" t="n">
+        <v>104</v>
+      </c>
+      <c r="V12" t="n">
+        <v>70.43000000000001</v>
+      </c>
+      <c r="W12" t="n">
+        <v>6</v>
+      </c>
+      <c r="X12" t="n">
+        <v>114</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>48.63</v>
       </c>
       <c r="Z12" s="1" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA12" s="1" t="n">
-        <v>1431</v>
+        <v>150</v>
       </c>
       <c r="AB12" s="1" t="n">
-        <v>-0</v>
+        <v>42.34</v>
       </c>
       <c r="AC12" s="1" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AD12" s="1" t="n">
-        <v>1372</v>
+        <v>184</v>
       </c>
       <c r="AE12" s="1" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>6</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>117</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>51.3</v>
+        <v>38.34</v>
+      </c>
+      <c r="AF12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" s="1" t="n">
+        <v>1332</v>
+      </c>
+      <c r="AH12" s="1" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="13">
@@ -1796,106 +1796,106 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>team0994</t>
+          <t>team0984</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>吴显熠</t>
+          <t>安澍</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>53.21</v>
-      </c>
-      <c r="E13" t="n">
-        <v>6</v>
-      </c>
-      <c r="F13" t="n">
-        <v>167</v>
-      </c>
-      <c r="G13" t="n">
-        <v>47.55</v>
+        <v>51.86</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>345</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>37.59</v>
       </c>
       <c r="H13" t="n">
         <v>6</v>
       </c>
       <c r="I13" t="n">
-        <v>158</v>
+        <v>239</v>
       </c>
       <c r="J13" t="n">
-        <v>48.23</v>
+        <v>50.19</v>
       </c>
       <c r="K13" t="n">
         <v>6</v>
       </c>
       <c r="L13" t="n">
-        <v>117</v>
+        <v>86</v>
       </c>
       <c r="M13" t="n">
-        <v>57</v>
+        <v>61.88</v>
       </c>
       <c r="N13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O13" t="n">
-        <v>92</v>
+        <v>150</v>
       </c>
       <c r="P13" t="n">
-        <v>53.17</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>6</v>
-      </c>
-      <c r="R13" t="n">
-        <v>109</v>
-      </c>
-      <c r="S13" t="n">
-        <v>51.9</v>
+        <v>43.5</v>
+      </c>
+      <c r="Q13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="T13" t="n">
         <v>7</v>
       </c>
       <c r="U13" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="V13" t="n">
-        <v>67.76000000000001</v>
+        <v>70.64</v>
       </c>
       <c r="W13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X13" t="n">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="Y13" t="n">
-        <v>46.84</v>
+        <v>58.93</v>
       </c>
       <c r="Z13" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA13" s="1" t="n">
+        <v>284</v>
+      </c>
+      <c r="AB13" s="1" t="n">
+        <v>26.59</v>
+      </c>
+      <c r="AC13" t="n">
         <v>4</v>
       </c>
-      <c r="AA13" s="1" t="n">
-        <v>150</v>
-      </c>
-      <c r="AB13" s="1" t="n">
-        <v>40.69</v>
-      </c>
-      <c r="AC13" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD13" s="1" t="n">
-        <v>184</v>
-      </c>
-      <c r="AE13" s="1" t="n">
-        <v>38.56</v>
-      </c>
-      <c r="AF13" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" s="1" t="n">
-        <v>1332</v>
-      </c>
-      <c r="AH13" s="1" t="n">
-        <v>-0</v>
+      <c r="AD13" t="n">
+        <v>155</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>40.19</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>190</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>37.66</v>
       </c>
     </row>
     <row r="14">
@@ -1904,106 +1904,106 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>team0984</t>
+          <t>team0973</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>安澍</t>
+          <t>罗鑫宇</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>49.51</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="F14" s="1" t="n">
-        <v>345</v>
-      </c>
-      <c r="G14" s="1" t="n">
-        <v>28.5</v>
+        <v>50.37</v>
+      </c>
+      <c r="E14" t="n">
+        <v>6</v>
+      </c>
+      <c r="F14" t="n">
+        <v>192</v>
+      </c>
+      <c r="G14" t="n">
+        <v>51.73</v>
       </c>
       <c r="H14" t="n">
         <v>6</v>
       </c>
       <c r="I14" t="n">
-        <v>239</v>
+        <v>201</v>
       </c>
       <c r="J14" t="n">
-        <v>42.15</v>
+        <v>51.76</v>
       </c>
       <c r="K14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L14" t="n">
-        <v>86</v>
+        <v>318</v>
       </c>
       <c r="M14" t="n">
-        <v>59.58</v>
-      </c>
-      <c r="N14" t="n">
-        <v>5</v>
-      </c>
-      <c r="O14" t="n">
-        <v>150</v>
-      </c>
-      <c r="P14" t="n">
         <v>40.69</v>
       </c>
-      <c r="Q14" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" s="1" t="n">
-        <v>0</v>
+      <c r="N14" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O14" s="1" t="n">
+        <v>321</v>
+      </c>
+      <c r="P14" s="1" t="n">
+        <v>28.83</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>5</v>
+      </c>
+      <c r="R14" t="n">
+        <v>221</v>
+      </c>
+      <c r="S14" t="n">
+        <v>40.37</v>
       </c>
       <c r="T14" t="n">
         <v>7</v>
       </c>
       <c r="U14" t="n">
-        <v>101</v>
+        <v>68</v>
       </c>
       <c r="V14" t="n">
-        <v>68.06</v>
-      </c>
-      <c r="W14" t="n">
-        <v>7</v>
-      </c>
-      <c r="X14" t="n">
-        <v>78</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>57.51</v>
+        <v>73</v>
+      </c>
+      <c r="W14" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" s="1" t="n">
+        <v>1472</v>
+      </c>
+      <c r="Y14" s="1" t="n">
+        <v>-0</v>
       </c>
       <c r="Z14" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA14" s="1" t="n">
-        <v>284</v>
+        <v>1428</v>
       </c>
       <c r="AB14" s="1" t="n">
-        <v>24.23</v>
+        <v>-0</v>
       </c>
       <c r="AC14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AD14" t="n">
-        <v>155</v>
+        <v>67</v>
       </c>
       <c r="AE14" t="n">
-        <v>40.38</v>
+        <v>57.25</v>
       </c>
       <c r="AF14" t="n">
         <v>5</v>
       </c>
       <c r="AG14" t="n">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="AH14" t="n">
-        <v>38.19</v>
+        <v>37.79</v>
       </c>
     </row>
     <row r="15">
@@ -2021,7 +2021,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>47.54</v>
+        <v>49.74</v>
       </c>
       <c r="E15" s="1" t="n">
         <v>0</v>
@@ -2048,7 +2048,7 @@
         <v>211</v>
       </c>
       <c r="M15" t="n">
-        <v>40.97</v>
+        <v>45.71</v>
       </c>
       <c r="N15" s="1" t="n">
         <v>4</v>
@@ -2057,7 +2057,7 @@
         <v>317</v>
       </c>
       <c r="P15" s="1" t="n">
-        <v>24.2</v>
+        <v>28.97</v>
       </c>
       <c r="Q15" t="n">
         <v>7</v>
@@ -2066,7 +2066,7 @@
         <v>85</v>
       </c>
       <c r="S15" t="n">
-        <v>62.65</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="T15" t="n">
         <v>6</v>
@@ -2075,7 +2075,7 @@
         <v>213</v>
       </c>
       <c r="V15" t="n">
-        <v>49</v>
+        <v>53.7</v>
       </c>
       <c r="W15" t="n">
         <v>5</v>
@@ -2084,7 +2084,7 @@
         <v>225</v>
       </c>
       <c r="Y15" t="n">
-        <v>32.73</v>
+        <v>35.68</v>
       </c>
       <c r="Z15" t="n">
         <v>4</v>
@@ -2093,7 +2093,7 @@
         <v>124</v>
       </c>
       <c r="AB15" t="n">
-        <v>42.31</v>
+        <v>43.68</v>
       </c>
       <c r="AC15" t="n">
         <v>5</v>
@@ -2102,7 +2102,7 @@
         <v>119</v>
       </c>
       <c r="AE15" t="n">
-        <v>53.28</v>
+        <v>53.11</v>
       </c>
       <c r="AF15" t="n">
         <v>6</v>
@@ -2111,7 +2111,7 @@
         <v>110</v>
       </c>
       <c r="AH15" t="n">
-        <v>51.82</v>
+        <v>51.46</v>
       </c>
     </row>
     <row r="16">
@@ -2120,106 +2120,106 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>team0973</t>
+          <t>team0986</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>罗鑫宇</t>
+          <t>丁有艺</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>46.77</v>
+        <v>49.71</v>
       </c>
       <c r="E16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F16" t="n">
-        <v>192</v>
+        <v>356</v>
       </c>
       <c r="G16" t="n">
-        <v>45.67</v>
+        <v>37.19</v>
       </c>
       <c r="H16" t="n">
         <v>6</v>
       </c>
       <c r="I16" t="n">
-        <v>201</v>
+        <v>248</v>
       </c>
       <c r="J16" t="n">
-        <v>45</v>
+        <v>49.82</v>
       </c>
       <c r="K16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L16" t="n">
-        <v>318</v>
+        <v>131</v>
       </c>
       <c r="M16" t="n">
-        <v>33.54</v>
+        <v>59.35</v>
       </c>
       <c r="N16" s="1" t="n">
         <v>4</v>
       </c>
       <c r="O16" s="1" t="n">
-        <v>321</v>
+        <v>393</v>
       </c>
       <c r="P16" s="1" t="n">
-        <v>24</v>
+        <v>26.32</v>
       </c>
       <c r="Q16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R16" t="n">
-        <v>221</v>
+        <v>175</v>
       </c>
       <c r="S16" t="n">
-        <v>36.25</v>
+        <v>50.86</v>
       </c>
       <c r="T16" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U16" t="n">
-        <v>68</v>
+        <v>164</v>
       </c>
       <c r="V16" t="n">
-        <v>71.26000000000001</v>
+        <v>56.7</v>
       </c>
       <c r="W16" s="1" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X16" s="1" t="n">
-        <v>1472</v>
+        <v>274</v>
       </c>
       <c r="Y16" s="1" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Z16" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA16" s="1" t="n">
-        <v>1428</v>
-      </c>
-      <c r="AB16" s="1" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>67</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>57.34</v>
+        <v>33.55</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>187</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>40.44</v>
+      </c>
+      <c r="AC16" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD16" s="1" t="n">
+        <v>205</v>
+      </c>
+      <c r="AE16" s="1" t="n">
+        <v>37.01</v>
       </c>
       <c r="AF16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG16" t="n">
-        <v>188</v>
+        <v>83</v>
       </c>
       <c r="AH16" t="n">
-        <v>38.31</v>
+        <v>53.58</v>
       </c>
     </row>
     <row r="17">
@@ -2228,106 +2228,106 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>team0986</t>
+          <t>team0988</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>丁有艺</t>
+          <t>吴宗阳</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>46.69</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="F17" s="1" t="n">
-        <v>356</v>
-      </c>
-      <c r="G17" s="1" t="n">
-        <v>27.81</v>
+        <v>49.28</v>
+      </c>
+      <c r="E17" t="n">
+        <v>6</v>
+      </c>
+      <c r="F17" t="n">
+        <v>135</v>
+      </c>
+      <c r="G17" t="n">
+        <v>54.2</v>
       </c>
       <c r="H17" t="n">
         <v>6</v>
       </c>
       <c r="I17" t="n">
-        <v>248</v>
+        <v>306</v>
       </c>
       <c r="J17" t="n">
-        <v>41.48</v>
+        <v>47.43</v>
       </c>
       <c r="K17" t="n">
+        <v>5</v>
+      </c>
+      <c r="L17" t="n">
+        <v>216</v>
+      </c>
+      <c r="M17" t="n">
+        <v>45.48</v>
+      </c>
+      <c r="N17" t="n">
         <v>6</v>
       </c>
-      <c r="L17" t="n">
-        <v>131</v>
-      </c>
-      <c r="M17" t="n">
-        <v>55.83</v>
-      </c>
-      <c r="N17" s="1" t="n">
+      <c r="O17" t="n">
+        <v>86</v>
+      </c>
+      <c r="P17" t="n">
+        <v>55.55</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>5</v>
+      </c>
+      <c r="R17" t="n">
+        <v>260</v>
+      </c>
+      <c r="S17" t="n">
+        <v>38.66</v>
+      </c>
+      <c r="T17" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" s="1" t="n">
+        <v>821</v>
+      </c>
+      <c r="V17" s="1" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W17" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="O17" s="1" t="n">
-        <v>393</v>
-      </c>
-      <c r="P17" s="1" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>6</v>
-      </c>
-      <c r="R17" t="n">
-        <v>175</v>
-      </c>
-      <c r="S17" t="n">
-        <v>46.95</v>
-      </c>
-      <c r="T17" t="n">
-        <v>6</v>
-      </c>
-      <c r="U17" t="n">
-        <v>164</v>
-      </c>
-      <c r="V17" t="n">
-        <v>53.08</v>
-      </c>
-      <c r="W17" s="1" t="n">
-        <v>5</v>
-      </c>
       <c r="X17" s="1" t="n">
-        <v>274</v>
+        <v>364</v>
       </c>
       <c r="Y17" s="1" t="n">
-        <v>29.94</v>
+        <v>23.7</v>
       </c>
       <c r="Z17" t="n">
         <v>4</v>
       </c>
       <c r="AA17" t="n">
-        <v>187</v>
+        <v>227</v>
       </c>
       <c r="AB17" t="n">
-        <v>38.38</v>
-      </c>
-      <c r="AC17" t="n">
+        <v>38.39</v>
+      </c>
+      <c r="AC17" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="AD17" t="n">
-        <v>205</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>37.25</v>
+      <c r="AD17" s="1" t="n">
+        <v>390</v>
+      </c>
+      <c r="AE17" s="1" t="n">
+        <v>25.22</v>
       </c>
       <c r="AF17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG17" t="n">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="AH17" t="n">
-        <v>53.85</v>
+        <v>65.25</v>
       </c>
     </row>
     <row r="18">
@@ -2336,106 +2336,106 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>team0988</t>
+          <t>team1798</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>吴宗阳</t>
+          <t>李奕澎</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>45.21</v>
-      </c>
-      <c r="E18" t="n">
+        <v>46.41</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>5</v>
+      </c>
+      <c r="L18" t="n">
+        <v>332</v>
+      </c>
+      <c r="M18" t="n">
+        <v>40.04</v>
+      </c>
+      <c r="N18" t="n">
+        <v>5</v>
+      </c>
+      <c r="O18" t="n">
+        <v>192</v>
+      </c>
+      <c r="P18" t="n">
+        <v>41.67</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>5</v>
+      </c>
+      <c r="R18" t="n">
+        <v>256</v>
+      </c>
+      <c r="S18" t="n">
+        <v>38.84</v>
+      </c>
+      <c r="T18" t="n">
         <v>6</v>
       </c>
-      <c r="F18" t="n">
-        <v>135</v>
-      </c>
-      <c r="G18" t="n">
-        <v>49.95</v>
-      </c>
-      <c r="H18" t="n">
-        <v>6</v>
-      </c>
-      <c r="I18" t="n">
-        <v>306</v>
-      </c>
-      <c r="J18" t="n">
-        <v>37.12</v>
-      </c>
-      <c r="K18" t="n">
-        <v>5</v>
-      </c>
-      <c r="L18" t="n">
-        <v>216</v>
-      </c>
-      <c r="M18" t="n">
-        <v>40.62</v>
-      </c>
-      <c r="N18" t="n">
-        <v>6</v>
-      </c>
-      <c r="O18" t="n">
-        <v>86</v>
-      </c>
-      <c r="P18" t="n">
-        <v>53.62</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>5</v>
-      </c>
-      <c r="R18" t="n">
-        <v>260</v>
-      </c>
-      <c r="S18" t="n">
-        <v>33.81</v>
-      </c>
-      <c r="T18" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="U18" s="1" t="n">
-        <v>821</v>
-      </c>
-      <c r="V18" s="1" t="n">
-        <v>0</v>
+      <c r="U18" t="n">
+        <v>155</v>
+      </c>
+      <c r="V18" t="n">
+        <v>57.25</v>
       </c>
       <c r="W18" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X18" s="1" t="n">
-        <v>364</v>
+        <v>204</v>
       </c>
       <c r="Y18" s="1" t="n">
-        <v>19.86</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>227</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>35.88</v>
+        <v>36.6</v>
+      </c>
+      <c r="Z18" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA18" s="1" t="n">
+        <v>453</v>
+      </c>
+      <c r="AB18" s="1" t="n">
+        <v>20.08</v>
       </c>
       <c r="AC18" s="1" t="n">
         <v>4</v>
       </c>
       <c r="AD18" s="1" t="n">
-        <v>390</v>
+        <v>345</v>
       </c>
       <c r="AE18" s="1" t="n">
-        <v>25.69</v>
+        <v>28.09</v>
       </c>
       <c r="AF18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AG18" t="n">
-        <v>53</v>
+        <v>74</v>
       </c>
       <c r="AH18" t="n">
-        <v>65.45</v>
+        <v>54.28</v>
       </c>
     </row>
     <row r="19">
@@ -2444,106 +2444,106 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>team1798</t>
+          <t>team0999</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>李奕澎</t>
+          <t>胡恒瑞</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>42.88</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J19" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="L19" s="1" t="n">
+        <v>43.83</v>
+      </c>
+      <c r="E19" t="n">
+        <v>5</v>
+      </c>
+      <c r="F19" t="n">
         <v>332</v>
       </c>
-      <c r="M19" s="1" t="n">
-        <v>32.57</v>
-      </c>
-      <c r="N19" t="n">
-        <v>5</v>
-      </c>
-      <c r="O19" t="n">
-        <v>192</v>
-      </c>
-      <c r="P19" t="n">
+      <c r="G19" t="n">
         <v>38.06</v>
       </c>
+      <c r="H19" t="n">
+        <v>6</v>
+      </c>
+      <c r="I19" t="n">
+        <v>291</v>
+      </c>
+      <c r="J19" t="n">
+        <v>48.05</v>
+      </c>
+      <c r="K19" t="n">
+        <v>5</v>
+      </c>
+      <c r="L19" t="n">
+        <v>228</v>
+      </c>
+      <c r="M19" t="n">
+        <v>44.91</v>
+      </c>
+      <c r="N19" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="O19" s="1" t="n">
+        <v>395</v>
+      </c>
+      <c r="P19" s="1" t="n">
+        <v>26.25</v>
+      </c>
       <c r="Q19" t="n">
         <v>5</v>
       </c>
       <c r="R19" t="n">
-        <v>256</v>
+        <v>285</v>
       </c>
       <c r="S19" t="n">
-        <v>34.06</v>
+        <v>37.57</v>
       </c>
       <c r="T19" t="n">
         <v>6</v>
       </c>
       <c r="U19" t="n">
-        <v>155</v>
+        <v>224</v>
       </c>
       <c r="V19" t="n">
-        <v>53.83</v>
+        <v>53.03</v>
       </c>
       <c r="W19" t="n">
         <v>5</v>
       </c>
       <c r="X19" t="n">
-        <v>204</v>
+        <v>296</v>
       </c>
       <c r="Y19" t="n">
-        <v>33.92</v>
+        <v>32.59</v>
       </c>
       <c r="Z19" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA19" s="1" t="n">
-        <v>453</v>
+        <v>1443</v>
       </c>
       <c r="AB19" s="1" t="n">
-        <v>16.31</v>
-      </c>
-      <c r="AC19" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD19" s="1" t="n">
-        <v>345</v>
-      </c>
-      <c r="AE19" s="1" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>6</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>74</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>54.52</v>
+        <v>-0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>125</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>52.63</v>
+      </c>
+      <c r="AF19" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG19" s="1" t="n">
+        <v>543</v>
+      </c>
+      <c r="AH19" s="1" t="n">
+        <v>5.85</v>
       </c>
     </row>
     <row r="20">
@@ -2552,106 +2552,106 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>team0977</t>
+          <t>team0989</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>丁培钊</t>
+          <t>谢兆轩</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>39.97</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="F20" s="1" t="n">
-        <v>761</v>
-      </c>
-      <c r="G20" s="1" t="n">
-        <v>1.5</v>
+        <v>43.77</v>
+      </c>
+      <c r="E20" t="n">
+        <v>5</v>
+      </c>
+      <c r="F20" t="n">
+        <v>263</v>
+      </c>
+      <c r="G20" t="n">
+        <v>40.55</v>
       </c>
       <c r="H20" t="n">
         <v>6</v>
       </c>
       <c r="I20" t="n">
-        <v>243</v>
+        <v>341</v>
       </c>
       <c r="J20" t="n">
-        <v>41.85</v>
+        <v>45.99</v>
       </c>
       <c r="K20" t="n">
         <v>5</v>
       </c>
       <c r="L20" t="n">
-        <v>194</v>
+        <v>333</v>
       </c>
       <c r="M20" t="n">
-        <v>42.15</v>
+        <v>39.99</v>
       </c>
       <c r="N20" t="n">
         <v>5</v>
       </c>
       <c r="O20" t="n">
-        <v>184</v>
+        <v>205</v>
       </c>
       <c r="P20" t="n">
-        <v>38.56</v>
+        <v>41.1</v>
       </c>
       <c r="Q20" t="n">
+        <v>5</v>
+      </c>
+      <c r="R20" t="n">
+        <v>347</v>
+      </c>
+      <c r="S20" t="n">
+        <v>34.85</v>
+      </c>
+      <c r="T20" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="U20" s="1" t="n">
+        <v>505</v>
+      </c>
+      <c r="V20" s="1" t="n">
+        <v>23.89</v>
+      </c>
+      <c r="W20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" s="1" t="n">
+        <v>1479</v>
+      </c>
+      <c r="Y20" s="1" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z20" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="1" t="n">
+        <v>1436</v>
+      </c>
+      <c r="AB20" s="1" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>134</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>51.91</v>
+      </c>
+      <c r="AF20" t="n">
         <v>6</v>
       </c>
-      <c r="R20" t="n">
-        <v>145</v>
-      </c>
-      <c r="S20" t="n">
-        <v>49.2</v>
-      </c>
-      <c r="T20" t="n">
-        <v>5</v>
-      </c>
-      <c r="U20" t="n">
-        <v>294</v>
-      </c>
-      <c r="V20" t="n">
-        <v>35.21</v>
-      </c>
-      <c r="W20" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="X20" s="1" t="n">
-        <v>261</v>
-      </c>
-      <c r="Y20" s="1" t="n">
-        <v>30.68</v>
-      </c>
-      <c r="Z20" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA20" s="1" t="n">
-        <v>310</v>
-      </c>
-      <c r="AB20" s="1" t="n">
-        <v>23.02</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>264</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>33.56</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>5</v>
-      </c>
       <c r="AG20" t="n">
-        <v>173</v>
+        <v>103</v>
       </c>
       <c r="AH20" t="n">
-        <v>39.25</v>
+        <v>52.01</v>
       </c>
     </row>
     <row r="21">
@@ -2660,106 +2660,106 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>team0989</t>
+          <t>team0977</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>谢兆轩</t>
+          <t>丁培钊</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>38.67</v>
-      </c>
-      <c r="E21" t="n">
-        <v>5</v>
-      </c>
-      <c r="F21" t="n">
-        <v>263</v>
-      </c>
-      <c r="G21" t="n">
-        <v>33.62</v>
+        <v>43.5</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="F21" s="1" t="n">
+        <v>761</v>
+      </c>
+      <c r="G21" s="1" t="n">
+        <v>13.55</v>
       </c>
       <c r="H21" t="n">
         <v>6</v>
       </c>
       <c r="I21" t="n">
-        <v>341</v>
+        <v>243</v>
       </c>
       <c r="J21" t="n">
-        <v>34.5</v>
+        <v>50.03</v>
       </c>
       <c r="K21" t="n">
         <v>5</v>
       </c>
       <c r="L21" t="n">
-        <v>333</v>
+        <v>194</v>
       </c>
       <c r="M21" t="n">
-        <v>32.5</v>
+        <v>46.51</v>
       </c>
       <c r="N21" t="n">
         <v>5</v>
       </c>
       <c r="O21" t="n">
-        <v>205</v>
+        <v>184</v>
       </c>
       <c r="P21" t="n">
-        <v>37.25</v>
+        <v>42.02</v>
       </c>
       <c r="Q21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R21" t="n">
-        <v>347</v>
+        <v>145</v>
       </c>
       <c r="S21" t="n">
-        <v>28.38</v>
-      </c>
-      <c r="T21" s="1" t="n">
+        <v>52.43</v>
+      </c>
+      <c r="T21" t="n">
+        <v>5</v>
+      </c>
+      <c r="U21" t="n">
+        <v>294</v>
+      </c>
+      <c r="V21" t="n">
+        <v>40.62</v>
+      </c>
+      <c r="W21" t="n">
+        <v>5</v>
+      </c>
+      <c r="X21" t="n">
+        <v>261</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>34.11</v>
+      </c>
+      <c r="Z21" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA21" s="1" t="n">
+        <v>310</v>
+      </c>
+      <c r="AB21" s="1" t="n">
+        <v>25.59</v>
+      </c>
+      <c r="AC21" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="U21" s="1" t="n">
-        <v>505</v>
-      </c>
-      <c r="V21" s="1" t="n">
-        <v>16.44</v>
-      </c>
-      <c r="W21" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" s="1" t="n">
-        <v>1479</v>
-      </c>
-      <c r="Y21" s="1" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Z21" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" s="1" t="n">
-        <v>1436</v>
-      </c>
-      <c r="AB21" s="1" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>134</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>52.11</v>
+      <c r="AD21" s="1" t="n">
+        <v>264</v>
+      </c>
+      <c r="AE21" s="1" t="n">
+        <v>33.25</v>
       </c>
       <c r="AF21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG21" t="n">
-        <v>103</v>
+        <v>173</v>
       </c>
       <c r="AH21" t="n">
-        <v>52.35</v>
+        <v>38.77</v>
       </c>
     </row>
     <row r="22">
@@ -2768,106 +2768,106 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>team0999</t>
+          <t>team0971</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>胡恒瑞</t>
+          <t>安奕轩</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>38.46</v>
-      </c>
-      <c r="E22" t="n">
-        <v>5</v>
-      </c>
-      <c r="F22" t="n">
-        <v>332</v>
-      </c>
-      <c r="G22" t="n">
-        <v>29.31</v>
+        <v>41.47</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="F22" s="1" t="n">
+        <v>648</v>
+      </c>
+      <c r="G22" s="1" t="n">
+        <v>21.33</v>
       </c>
       <c r="H22" t="n">
         <v>6</v>
       </c>
       <c r="I22" t="n">
-        <v>291</v>
+        <v>270</v>
       </c>
       <c r="J22" t="n">
-        <v>38.25</v>
+        <v>48.91</v>
       </c>
       <c r="K22" t="n">
         <v>5</v>
       </c>
       <c r="L22" t="n">
-        <v>228</v>
+        <v>334</v>
       </c>
       <c r="M22" t="n">
-        <v>39.79</v>
-      </c>
-      <c r="N22" s="1" t="n">
+        <v>39.94</v>
+      </c>
+      <c r="N22" t="n">
+        <v>6</v>
+      </c>
+      <c r="O22" t="n">
+        <v>78</v>
+      </c>
+      <c r="P22" t="n">
+        <v>55.97</v>
+      </c>
+      <c r="Q22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" s="1" t="n">
+        <v>1513</v>
+      </c>
+      <c r="S22" s="1" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T22" t="n">
         <v>4</v>
       </c>
-      <c r="O22" s="1" t="n">
-        <v>395</v>
-      </c>
-      <c r="P22" s="1" t="n">
-        <v>20.3</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>5</v>
-      </c>
-      <c r="R22" t="n">
-        <v>285</v>
-      </c>
-      <c r="S22" t="n">
-        <v>32.25</v>
-      </c>
-      <c r="T22" t="n">
+      <c r="U22" t="n">
+        <v>439</v>
+      </c>
+      <c r="V22" t="n">
+        <v>26.59</v>
+      </c>
+      <c r="W22" t="n">
         <v>6</v>
       </c>
-      <c r="U22" t="n">
-        <v>224</v>
-      </c>
-      <c r="V22" t="n">
-        <v>48.08</v>
-      </c>
-      <c r="W22" t="n">
-        <v>5</v>
-      </c>
       <c r="X22" t="n">
-        <v>296</v>
+        <v>147</v>
       </c>
       <c r="Y22" t="n">
-        <v>28.69</v>
-      </c>
-      <c r="Z22" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="1" t="n">
-        <v>1443</v>
-      </c>
-      <c r="AB22" s="1" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>125</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>52.81</v>
-      </c>
-      <c r="AF22" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG22" s="1" t="n">
-        <v>543</v>
-      </c>
-      <c r="AH22" s="1" t="n">
-        <v>6.45</v>
+        <v>46.9</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>417</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>21.47</v>
+      </c>
+      <c r="AC22" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="1" t="n">
+        <v>1369</v>
+      </c>
+      <c r="AE22" s="1" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>122</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>50.52</v>
       </c>
     </row>
     <row r="23">
@@ -2885,7 +2885,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>38.3</v>
+        <v>41.06</v>
       </c>
       <c r="E23" s="1" t="n">
         <v>3</v>
@@ -2894,7 +2894,7 @@
         <v>923</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>0</v>
+        <v>10.04</v>
       </c>
       <c r="H23" s="1" t="n">
         <v>0</v>
@@ -2912,7 +2912,7 @@
         <v>212</v>
       </c>
       <c r="M23" t="n">
-        <v>40.9</v>
+        <v>45.66</v>
       </c>
       <c r="N23" t="n">
         <v>5</v>
@@ -2921,7 +2921,7 @@
         <v>127</v>
       </c>
       <c r="P23" t="n">
-        <v>42.12</v>
+        <v>44.5</v>
       </c>
       <c r="Q23" t="n">
         <v>5</v>
@@ -2930,7 +2930,7 @@
         <v>334</v>
       </c>
       <c r="S23" t="n">
-        <v>29.19</v>
+        <v>35.42</v>
       </c>
       <c r="T23" t="n">
         <v>7</v>
@@ -2939,7 +2939,7 @@
         <v>108</v>
       </c>
       <c r="V23" t="n">
-        <v>67.38</v>
+        <v>70.14</v>
       </c>
       <c r="W23" t="n">
         <v>5</v>
@@ -2948,16 +2948,16 @@
         <v>276</v>
       </c>
       <c r="Y23" t="n">
-        <v>29.83</v>
-      </c>
-      <c r="Z23" s="1" t="n">
+        <v>33.46</v>
+      </c>
+      <c r="Z23" t="n">
         <v>3</v>
       </c>
-      <c r="AA23" s="1" t="n">
+      <c r="AA23" t="n">
         <v>339</v>
       </c>
-      <c r="AB23" s="1" t="n">
-        <v>21.66</v>
+      <c r="AB23" t="n">
+        <v>24.47</v>
       </c>
       <c r="AC23" t="n">
         <v>4</v>
@@ -2966,16 +2966,16 @@
         <v>256</v>
       </c>
       <c r="AE23" t="n">
-        <v>34.06</v>
-      </c>
-      <c r="AF23" t="n">
+        <v>33.76</v>
+      </c>
+      <c r="AF23" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="AG23" t="n">
+      <c r="AG23" s="1" t="n">
         <v>309</v>
       </c>
-      <c r="AH23" t="n">
-        <v>24.6</v>
+      <c r="AH23" s="1" t="n">
+        <v>23.92</v>
       </c>
     </row>
     <row r="24">
@@ -2984,106 +2984,106 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>team0971</t>
+          <t>team0992</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>安奕轩</t>
+          <t>林锐思</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>37.16</v>
-      </c>
-      <c r="E24" s="1" t="n">
+        <v>40.31</v>
+      </c>
+      <c r="E24" t="n">
+        <v>5</v>
+      </c>
+      <c r="F24" t="n">
+        <v>383</v>
+      </c>
+      <c r="G24" t="n">
+        <v>36.22</v>
+      </c>
+      <c r="H24" t="n">
+        <v>5</v>
+      </c>
+      <c r="I24" t="n">
+        <v>506</v>
+      </c>
+      <c r="J24" t="n">
+        <v>32.66</v>
+      </c>
+      <c r="K24" t="n">
+        <v>5</v>
+      </c>
+      <c r="L24" t="n">
+        <v>316</v>
+      </c>
+      <c r="M24" t="n">
+        <v>40.79</v>
+      </c>
+      <c r="N24" t="n">
         <v>4</v>
       </c>
-      <c r="F24" s="1" t="n">
-        <v>648</v>
-      </c>
-      <c r="G24" s="1" t="n">
-        <v>7.65</v>
-      </c>
-      <c r="H24" t="n">
+      <c r="O24" t="n">
+        <v>404</v>
+      </c>
+      <c r="P24" t="n">
+        <v>25.93</v>
+      </c>
+      <c r="Q24" t="n">
         <v>6</v>
       </c>
-      <c r="I24" t="n">
-        <v>270</v>
-      </c>
-      <c r="J24" t="n">
-        <v>39.82</v>
-      </c>
-      <c r="K24" t="n">
-        <v>5</v>
-      </c>
-      <c r="L24" t="n">
-        <v>334</v>
-      </c>
-      <c r="M24" t="n">
-        <v>32.43</v>
-      </c>
-      <c r="N24" t="n">
-        <v>6</v>
-      </c>
-      <c r="O24" t="n">
-        <v>78</v>
-      </c>
-      <c r="P24" t="n">
-        <v>54.23</v>
-      </c>
-      <c r="Q24" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" s="1" t="n">
-        <v>1513</v>
-      </c>
-      <c r="S24" s="1" t="n">
-        <v>-0</v>
+      <c r="R24" t="n">
+        <v>133</v>
+      </c>
+      <c r="S24" t="n">
+        <v>53.06</v>
       </c>
       <c r="T24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U24" t="n">
-        <v>439</v>
+        <v>291</v>
       </c>
       <c r="V24" t="n">
-        <v>20.11</v>
-      </c>
-      <c r="W24" t="n">
-        <v>6</v>
-      </c>
-      <c r="X24" t="n">
-        <v>147</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>44.59</v>
-      </c>
-      <c r="Z24" t="n">
+        <v>40.77</v>
+      </c>
+      <c r="W24" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" s="1" t="n">
+        <v>1481</v>
+      </c>
+      <c r="Y24" s="1" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z24" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="1" t="n">
+        <v>1439</v>
+      </c>
+      <c r="AB24" s="1" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>124</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>52.71</v>
+      </c>
+      <c r="AF24" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="AA24" t="n">
-        <v>417</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>18</v>
-      </c>
-      <c r="AC24" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD24" s="1" t="n">
-        <v>1369</v>
-      </c>
-      <c r="AE24" s="1" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>6</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>122</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>50.92</v>
+      <c r="AG24" s="1" t="n">
+        <v>453</v>
+      </c>
+      <c r="AH24" s="1" t="n">
+        <v>12.3</v>
       </c>
     </row>
     <row r="25">
@@ -3092,85 +3092,85 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>team0985</t>
+          <t>team0972</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>李子俊</t>
+          <t>刘芯羽</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>35.08</v>
+        <v>35.95</v>
       </c>
       <c r="E25" t="n">
         <v>5</v>
       </c>
       <c r="F25" t="n">
-        <v>458</v>
+        <v>426</v>
       </c>
       <c r="G25" t="n">
-        <v>21.44</v>
-      </c>
-      <c r="H25" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I25" s="1" t="n">
+        <v>34.67</v>
+      </c>
+      <c r="H25" t="n">
+        <v>5</v>
+      </c>
+      <c r="I25" t="n">
+        <v>444</v>
+      </c>
+      <c r="J25" t="n">
+        <v>34.79</v>
+      </c>
+      <c r="K25" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="L25" s="1" t="n">
+        <v>591</v>
+      </c>
+      <c r="M25" s="1" t="n">
+        <v>16.74</v>
+      </c>
+      <c r="N25" t="n">
+        <v>5</v>
+      </c>
+      <c r="O25" t="n">
+        <v>228</v>
+      </c>
+      <c r="P25" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>6</v>
+      </c>
+      <c r="R25" t="n">
+        <v>184</v>
+      </c>
+      <c r="S25" t="n">
+        <v>50.39</v>
+      </c>
+      <c r="T25" t="n">
+        <v>4</v>
+      </c>
+      <c r="U25" t="n">
+        <v>555</v>
+      </c>
+      <c r="V25" t="n">
+        <v>21.86</v>
+      </c>
+      <c r="W25" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" s="1" t="n">
+        <v>1471</v>
+      </c>
+      <c r="Y25" s="1" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z25" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="1" t="n">
         <v>1427</v>
-      </c>
-      <c r="J25" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" t="n">
-        <v>5</v>
-      </c>
-      <c r="O25" t="n">
-        <v>224</v>
-      </c>
-      <c r="P25" t="n">
-        <v>36.06</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>5</v>
-      </c>
-      <c r="R25" t="n">
-        <v>369</v>
-      </c>
-      <c r="S25" t="n">
-        <v>27</v>
-      </c>
-      <c r="T25" t="n">
-        <v>7</v>
-      </c>
-      <c r="U25" t="n">
-        <v>138</v>
-      </c>
-      <c r="V25" t="n">
-        <v>64.45999999999999</v>
-      </c>
-      <c r="W25" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" s="1" t="n">
-        <v>1478</v>
-      </c>
-      <c r="Y25" s="1" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Z25" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA25" s="1" t="n">
-        <v>1435</v>
       </c>
       <c r="AB25" s="1" t="n">
         <v>-0</v>
@@ -3179,19 +3179,19 @@
         <v>4</v>
       </c>
       <c r="AD25" t="n">
-        <v>378</v>
+        <v>290</v>
       </c>
       <c r="AE25" t="n">
-        <v>26.44</v>
-      </c>
-      <c r="AF25" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG25" s="1" t="n">
-        <v>1328</v>
-      </c>
-      <c r="AH25" s="1" t="n">
-        <v>-0</v>
+        <v>31.59</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>181</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>38.25</v>
       </c>
     </row>
     <row r="26">
@@ -3200,106 +3200,106 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>team0992</t>
+          <t>team0983</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>林锐思</t>
+          <t>周一鸣</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>33.79</v>
+        <v>34.39</v>
       </c>
       <c r="E26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F26" t="n">
-        <v>383</v>
+        <v>159</v>
       </c>
       <c r="G26" t="n">
-        <v>26.12</v>
+        <v>53.16</v>
       </c>
       <c r="H26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I26" t="n">
-        <v>506</v>
+        <v>377</v>
       </c>
       <c r="J26" t="n">
-        <v>18.44</v>
-      </c>
-      <c r="K26" t="n">
-        <v>5</v>
-      </c>
-      <c r="L26" t="n">
-        <v>316</v>
-      </c>
-      <c r="M26" t="n">
-        <v>33.68</v>
+        <v>44.51</v>
+      </c>
+      <c r="K26" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="N26" t="n">
         <v>4</v>
       </c>
       <c r="O26" t="n">
-        <v>404</v>
+        <v>473</v>
       </c>
       <c r="P26" t="n">
-        <v>19.85</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>6</v>
-      </c>
-      <c r="R26" t="n">
-        <v>133</v>
-      </c>
-      <c r="S26" t="n">
-        <v>50.1</v>
+        <v>23.53</v>
+      </c>
+      <c r="Q26" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="T26" t="n">
         <v>5</v>
       </c>
       <c r="U26" t="n">
-        <v>291</v>
+        <v>412</v>
       </c>
       <c r="V26" t="n">
-        <v>35.42</v>
-      </c>
-      <c r="W26" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" s="1" t="n">
-        <v>1481</v>
-      </c>
-      <c r="Y26" s="1" t="n">
-        <v>-0</v>
+        <v>34.61</v>
+      </c>
+      <c r="W26" t="n">
+        <v>5</v>
+      </c>
+      <c r="X26" t="n">
+        <v>262</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>34.07</v>
       </c>
       <c r="Z26" s="1" t="n">
         <v>0</v>
       </c>
       <c r="AA26" s="1" t="n">
-        <v>1439</v>
+        <v>1434</v>
       </c>
       <c r="AB26" s="1" t="n">
         <v>-0</v>
       </c>
       <c r="AC26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AD26" t="n">
-        <v>124</v>
+        <v>360</v>
       </c>
       <c r="AE26" t="n">
-        <v>52.89</v>
-      </c>
-      <c r="AF26" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG26" s="1" t="n">
-        <v>453</v>
-      </c>
-      <c r="AH26" s="1" t="n">
-        <v>13.05</v>
+        <v>27.13</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>313</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>23.71</v>
       </c>
     </row>
     <row r="27">
@@ -3308,106 +3308,106 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>team1006</t>
+          <t>team0967</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>徐嘉晨</t>
+          <t>杨鑫</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>31.47</v>
+        <v>33.43</v>
       </c>
       <c r="E27" t="n">
+        <v>5</v>
+      </c>
+      <c r="F27" t="n">
+        <v>472</v>
+      </c>
+      <c r="G27" t="n">
+        <v>33.01</v>
+      </c>
+      <c r="H27" t="n">
+        <v>5</v>
+      </c>
+      <c r="I27" t="n">
+        <v>448</v>
+      </c>
+      <c r="J27" t="n">
+        <v>34.65</v>
+      </c>
+      <c r="K27" t="n">
+        <v>5</v>
+      </c>
+      <c r="L27" t="n">
+        <v>247</v>
+      </c>
+      <c r="M27" t="n">
+        <v>44.02</v>
+      </c>
+      <c r="N27" t="n">
         <v>3</v>
       </c>
-      <c r="F27" t="n">
-        <v>780</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="H27" t="n">
+      <c r="O27" t="n">
+        <v>698</v>
+      </c>
+      <c r="P27" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>5</v>
+      </c>
+      <c r="R27" t="n">
+        <v>258</v>
+      </c>
+      <c r="S27" t="n">
+        <v>38.75</v>
+      </c>
+      <c r="T27" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" s="1" t="n">
+        <v>1487</v>
+      </c>
+      <c r="V27" s="1" t="n">
+        <v>-0</v>
+      </c>
+      <c r="W27" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" s="1" t="n">
+        <v>1467</v>
+      </c>
+      <c r="Y27" s="1" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z27" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="1" t="n">
+        <v>1424</v>
+      </c>
+      <c r="AB27" s="1" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC27" t="n">
         <v>4</v>
       </c>
-      <c r="I27" t="n">
-        <v>674</v>
-      </c>
-      <c r="J27" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="K27" t="n">
-        <v>4</v>
-      </c>
-      <c r="L27" t="n">
-        <v>438</v>
-      </c>
-      <c r="M27" t="n">
-        <v>20.17</v>
-      </c>
-      <c r="N27" t="n">
-        <v>4</v>
-      </c>
-      <c r="O27" t="n">
-        <v>261</v>
-      </c>
-      <c r="P27" t="n">
-        <v>27</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>7</v>
-      </c>
-      <c r="R27" t="n">
-        <v>40</v>
-      </c>
-      <c r="S27" t="n">
-        <v>66.59</v>
-      </c>
-      <c r="T27" t="n">
-        <v>7</v>
-      </c>
-      <c r="U27" t="n">
-        <v>102</v>
-      </c>
-      <c r="V27" t="n">
-        <v>67.95999999999999</v>
-      </c>
-      <c r="W27" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA27" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB27" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC27" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD27" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE27" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF27" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG27" s="1" t="n">
-        <v>1337</v>
-      </c>
-      <c r="AH27" s="1" t="n">
-        <v>-0</v>
+      <c r="AD27" t="n">
+        <v>236</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>35.03</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>203</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>36.81</v>
       </c>
     </row>
     <row r="28">
@@ -3416,106 +3416,106 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>team0972</t>
+          <t>team0998</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>刘芯羽</t>
+          <t>张哲源</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>30.31</v>
+        <v>32.04</v>
       </c>
       <c r="E28" t="n">
         <v>5</v>
       </c>
       <c r="F28" t="n">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="G28" t="n">
-        <v>23.44</v>
-      </c>
-      <c r="H28" t="n">
-        <v>5</v>
-      </c>
-      <c r="I28" t="n">
-        <v>444</v>
-      </c>
-      <c r="J28" t="n">
-        <v>22.31</v>
-      </c>
-      <c r="K28" s="1" t="n">
+        <v>35.21</v>
+      </c>
+      <c r="H28" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="I28" s="1" t="n">
+        <v>914</v>
+      </c>
+      <c r="J28" s="1" t="n">
+        <v>14.92</v>
+      </c>
+      <c r="K28" t="n">
+        <v>5</v>
+      </c>
+      <c r="L28" t="n">
+        <v>223</v>
+      </c>
+      <c r="M28" t="n">
+        <v>45.15</v>
+      </c>
+      <c r="N28" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="L28" s="1" t="n">
-        <v>591</v>
-      </c>
-      <c r="M28" s="1" t="n">
-        <v>8.75</v>
-      </c>
-      <c r="N28" t="n">
-        <v>5</v>
-      </c>
-      <c r="O28" t="n">
-        <v>228</v>
-      </c>
-      <c r="P28" t="n">
-        <v>35.81</v>
+      <c r="O28" s="1" t="n">
+        <v>671</v>
+      </c>
+      <c r="P28" s="1" t="n">
+        <v>12.46</v>
       </c>
       <c r="Q28" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R28" t="n">
-        <v>184</v>
+        <v>572</v>
       </c>
       <c r="S28" t="n">
-        <v>46.27</v>
+        <v>20</v>
       </c>
       <c r="T28" t="n">
+        <v>5</v>
+      </c>
+      <c r="U28" t="n">
+        <v>293</v>
+      </c>
+      <c r="V28" t="n">
+        <v>40.67</v>
+      </c>
+      <c r="W28" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="X28" s="1" t="n">
+        <v>516</v>
+      </c>
+      <c r="Y28" s="1" t="n">
+        <v>13.79</v>
+      </c>
+      <c r="Z28" t="n">
         <v>4</v>
       </c>
-      <c r="U28" t="n">
-        <v>555</v>
-      </c>
-      <c r="V28" t="n">
-        <v>13.67</v>
-      </c>
-      <c r="W28" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="X28" s="1" t="n">
-        <v>1471</v>
-      </c>
-      <c r="Y28" s="1" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Z28" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA28" s="1" t="n">
-        <v>1427</v>
-      </c>
-      <c r="AB28" s="1" t="n">
-        <v>-0</v>
+      <c r="AA28" t="n">
+        <v>169</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>41.37</v>
       </c>
       <c r="AC28" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>432</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>16.91</v>
+      </c>
+      <c r="AF28" t="n">
         <v>4</v>
       </c>
-      <c r="AD28" t="n">
-        <v>290</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>31.94</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>5</v>
-      </c>
       <c r="AG28" t="n">
-        <v>181</v>
+        <v>289</v>
       </c>
       <c r="AH28" t="n">
-        <v>38.75</v>
+        <v>24.96</v>
       </c>
     </row>
     <row r="29">
@@ -3524,85 +3524,85 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>team0983</t>
+          <t>team0985</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>周一鸣</t>
+          <t>李子俊</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>29.42</v>
+        <v>28.84</v>
       </c>
       <c r="E29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F29" t="n">
-        <v>159</v>
+        <v>458</v>
       </c>
       <c r="G29" t="n">
-        <v>48.15</v>
+        <v>33.51</v>
       </c>
       <c r="H29" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I29" t="n">
-        <v>377</v>
+        <v>1427</v>
       </c>
       <c r="J29" t="n">
-        <v>31.8</v>
-      </c>
-      <c r="K29" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" s="1" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O29" t="n">
-        <v>473</v>
+        <v>224</v>
       </c>
       <c r="P29" t="n">
-        <v>16.4</v>
-      </c>
-      <c r="Q29" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" s="1" t="n">
-        <v>0</v>
+        <v>40.27</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>5</v>
+      </c>
+      <c r="R29" t="n">
+        <v>369</v>
+      </c>
+      <c r="S29" t="n">
+        <v>33.89</v>
       </c>
       <c r="T29" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U29" t="n">
-        <v>412</v>
+        <v>138</v>
       </c>
       <c r="V29" t="n">
-        <v>27.01</v>
-      </c>
-      <c r="W29" t="n">
-        <v>5</v>
-      </c>
-      <c r="X29" t="n">
-        <v>262</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>30.63</v>
+        <v>68</v>
+      </c>
+      <c r="W29" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" s="1" t="n">
+        <v>1478</v>
+      </c>
+      <c r="Y29" s="1" t="n">
+        <v>-0</v>
       </c>
       <c r="Z29" s="1" t="n">
         <v>0</v>
       </c>
       <c r="AA29" s="1" t="n">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="AB29" s="1" t="n">
         <v>-0</v>
@@ -3611,19 +3611,19 @@
         <v>4</v>
       </c>
       <c r="AD29" t="n">
-        <v>360</v>
+        <v>378</v>
       </c>
       <c r="AE29" t="n">
-        <v>27.56</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>313</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>24.4</v>
+        <v>25.99</v>
+      </c>
+      <c r="AF29" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" s="1" t="n">
+        <v>1328</v>
+      </c>
+      <c r="AH29" s="1" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="30">
@@ -3632,106 +3632,106 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>team0998</t>
+          <t>team1792</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>张哲源</t>
+          <t>许家铭</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>27.66</v>
-      </c>
-      <c r="E30" t="n">
-        <v>5</v>
-      </c>
-      <c r="F30" t="n">
-        <v>411</v>
-      </c>
-      <c r="G30" t="n">
-        <v>24.38</v>
+        <v>26.06</v>
+      </c>
+      <c r="E30" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="H30" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
         <v>4</v>
       </c>
-      <c r="I30" s="1" t="n">
-        <v>914</v>
-      </c>
-      <c r="J30" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
-        <v>5</v>
-      </c>
       <c r="L30" t="n">
-        <v>223</v>
+        <v>390</v>
       </c>
       <c r="M30" t="n">
-        <v>40.14</v>
+        <v>29.85</v>
       </c>
       <c r="N30" s="1" t="n">
         <v>3</v>
       </c>
       <c r="O30" s="1" t="n">
-        <v>671</v>
+        <v>651</v>
       </c>
       <c r="P30" s="1" t="n">
-        <v>4.88</v>
+        <v>12.98</v>
       </c>
       <c r="Q30" t="n">
+        <v>5</v>
+      </c>
+      <c r="R30" t="n">
+        <v>354</v>
+      </c>
+      <c r="S30" t="n">
+        <v>34.54</v>
+      </c>
+      <c r="T30" t="n">
         <v>4</v>
       </c>
-      <c r="R30" t="n">
-        <v>572</v>
-      </c>
-      <c r="S30" t="n">
-        <v>11.45</v>
-      </c>
-      <c r="T30" t="n">
-        <v>5</v>
-      </c>
       <c r="U30" t="n">
-        <v>293</v>
+        <v>479</v>
       </c>
       <c r="V30" t="n">
-        <v>35.28</v>
+        <v>24.95</v>
       </c>
       <c r="W30" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
         <v>3</v>
       </c>
-      <c r="X30" s="1" t="n">
-        <v>516</v>
-      </c>
-      <c r="Y30" s="1" t="n">
-        <v>9.720000000000001</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>4</v>
-      </c>
       <c r="AA30" t="n">
-        <v>169</v>
+        <v>317</v>
       </c>
       <c r="AB30" t="n">
-        <v>39.5</v>
-      </c>
-      <c r="AC30" t="n">
+        <v>25.32</v>
+      </c>
+      <c r="AC30" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
         <v>3</v>
       </c>
-      <c r="AD30" t="n">
-        <v>432</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>17.3</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>4</v>
-      </c>
       <c r="AG30" t="n">
-        <v>289</v>
+        <v>368</v>
       </c>
       <c r="AH30" t="n">
-        <v>25.6</v>
+        <v>15.63</v>
       </c>
     </row>
     <row r="31">
@@ -3740,106 +3740,106 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>team0967</t>
+          <t>team1794</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>杨鑫</t>
+          <t>成伟业</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>27.37</v>
-      </c>
-      <c r="E31" t="n">
-        <v>5</v>
-      </c>
-      <c r="F31" t="n">
-        <v>472</v>
-      </c>
-      <c r="G31" t="n">
-        <v>20.56</v>
-      </c>
-      <c r="H31" t="n">
-        <v>5</v>
-      </c>
-      <c r="I31" t="n">
-        <v>448</v>
-      </c>
-      <c r="J31" t="n">
-        <v>22.06</v>
+        <v>22.53</v>
+      </c>
+      <c r="E31" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="K31" t="n">
         <v>5</v>
       </c>
       <c r="L31" t="n">
-        <v>247</v>
+        <v>303</v>
       </c>
       <c r="M31" t="n">
-        <v>38.47</v>
+        <v>41.4</v>
       </c>
       <c r="N31" t="n">
         <v>3</v>
       </c>
       <c r="O31" t="n">
-        <v>698</v>
+        <v>546</v>
       </c>
       <c r="P31" t="n">
-        <v>3.86</v>
+        <v>15.73</v>
       </c>
       <c r="Q31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R31" t="n">
-        <v>258</v>
+        <v>627</v>
       </c>
       <c r="S31" t="n">
-        <v>33.94</v>
+        <v>18.07</v>
       </c>
       <c r="T31" s="1" t="n">
         <v>0</v>
       </c>
       <c r="U31" s="1" t="n">
-        <v>1487</v>
+        <v>0</v>
       </c>
       <c r="V31" s="1" t="n">
-        <v>-0</v>
-      </c>
-      <c r="W31" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" s="1" t="n">
-        <v>1467</v>
-      </c>
-      <c r="Y31" s="1" t="n">
-        <v>-0</v>
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>3</v>
+      </c>
+      <c r="X31" t="n">
+        <v>595</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>11.73</v>
       </c>
       <c r="Z31" s="1" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA31" s="1" t="n">
-        <v>1424</v>
+        <v>742</v>
       </c>
       <c r="AB31" s="1" t="n">
-        <v>-0</v>
+        <v>8.94</v>
       </c>
       <c r="AC31" t="n">
         <v>4</v>
       </c>
       <c r="AD31" t="n">
-        <v>236</v>
+        <v>382</v>
       </c>
       <c r="AE31" t="n">
-        <v>35.31</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>5</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>203</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>37.38</v>
+        <v>25.73</v>
+      </c>
+      <c r="AF31" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG31" s="1" t="n">
+        <v>665</v>
+      </c>
+      <c r="AH31" s="1" t="n">
+        <v>2.66</v>
       </c>
     </row>
     <row r="32">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>team1788</t>
+          <t>team1789</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>王义轩</t>
+          <t>魏胜新</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>27.18</v>
+        <v>20.9</v>
       </c>
       <c r="E32" s="1" t="n">
         <v>0</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="G32" s="1" t="n">
         <v>-0</v>
@@ -3872,82 +3872,82 @@
         <v>0</v>
       </c>
       <c r="I32" s="1" t="n">
-        <v>1869</v>
+        <v>1870</v>
       </c>
       <c r="J32" s="1" t="n">
         <v>-0</v>
       </c>
-      <c r="K32" s="1" t="n">
+      <c r="K32" t="n">
+        <v>3</v>
+      </c>
+      <c r="L32" t="n">
+        <v>726</v>
+      </c>
+      <c r="M32" t="n">
+        <v>12.94</v>
+      </c>
+      <c r="N32" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="L32" s="1" t="n">
-        <v>878</v>
-      </c>
-      <c r="M32" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" t="n">
+      <c r="O32" s="1" t="n">
+        <v>1030</v>
+      </c>
+      <c r="P32" s="1" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2</v>
+      </c>
+      <c r="R32" t="n">
+        <v>907</v>
+      </c>
+      <c r="S32" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="T32" t="n">
+        <v>5</v>
+      </c>
+      <c r="U32" t="n">
+        <v>399</v>
+      </c>
+      <c r="V32" t="n">
+        <v>35.27</v>
+      </c>
+      <c r="W32" t="n">
         <v>4</v>
       </c>
-      <c r="O32" t="n">
-        <v>387</v>
-      </c>
-      <c r="P32" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>5</v>
-      </c>
-      <c r="R32" t="n">
-        <v>366</v>
-      </c>
-      <c r="S32" t="n">
-        <v>27.19</v>
-      </c>
-      <c r="T32" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="U32" s="1" t="n">
-        <v>847</v>
-      </c>
-      <c r="V32" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z32" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA32" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB32" s="1" t="n">
-        <v>0</v>
+      <c r="X32" t="n">
+        <v>379</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>23.17</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>39.77</v>
       </c>
       <c r="AC32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AD32" t="n">
-        <v>219</v>
+        <v>498</v>
       </c>
       <c r="AE32" t="n">
-        <v>36.38</v>
+        <v>13.76</v>
       </c>
       <c r="AF32" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AG32" t="n">
-        <v>312</v>
+        <v>326</v>
       </c>
       <c r="AH32" t="n">
-        <v>24.45</v>
+        <v>17.27</v>
       </c>
     </row>
     <row r="33">
@@ -3956,106 +3956,106 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>team1792</t>
+          <t>team0968</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>许家铭</t>
+          <t>李健</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>21.52</v>
-      </c>
-      <c r="E33" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
+        <v>20.17</v>
+      </c>
+      <c r="E33" t="n">
+        <v>5</v>
+      </c>
+      <c r="F33" t="n">
+        <v>482</v>
+      </c>
+      <c r="G33" t="n">
+        <v>32.65</v>
+      </c>
+      <c r="H33" t="n">
+        <v>5</v>
+      </c>
+      <c r="I33" t="n">
+        <v>490</v>
+      </c>
+      <c r="J33" t="n">
+        <v>33.21</v>
+      </c>
+      <c r="K33" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L33" s="1" t="n">
+        <v>849</v>
+      </c>
+      <c r="M33" s="1" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="N33" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="O33" s="1" t="n">
+        <v>877</v>
+      </c>
+      <c r="P33" s="1" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="Q33" t="n">
         <v>4</v>
       </c>
-      <c r="L33" t="n">
-        <v>390</v>
-      </c>
-      <c r="M33" t="n">
-        <v>22.83</v>
-      </c>
-      <c r="N33" s="1" t="n">
+      <c r="R33" t="n">
+        <v>622</v>
+      </c>
+      <c r="S33" t="n">
+        <v>18.25</v>
+      </c>
+      <c r="T33" t="n">
         <v>3</v>
       </c>
-      <c r="O33" s="1" t="n">
-        <v>651</v>
-      </c>
-      <c r="P33" s="1" t="n">
-        <v>5.62</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>5</v>
-      </c>
-      <c r="R33" t="n">
-        <v>354</v>
-      </c>
-      <c r="S33" t="n">
-        <v>27.94</v>
-      </c>
-      <c r="T33" t="n">
-        <v>4</v>
-      </c>
       <c r="U33" t="n">
-        <v>479</v>
+        <v>696</v>
       </c>
       <c r="V33" t="n">
-        <v>17.89</v>
+        <v>12.08</v>
       </c>
       <c r="W33" s="1" t="n">
         <v>0</v>
       </c>
       <c r="X33" s="1" t="n">
-        <v>0</v>
+        <v>1468</v>
       </c>
       <c r="Y33" s="1" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z33" t="n">
         <v>3</v>
       </c>
       <c r="AA33" t="n">
-        <v>317</v>
+        <v>425</v>
       </c>
       <c r="AB33" t="n">
-        <v>22.69</v>
-      </c>
-      <c r="AC33" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD33" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE33" s="1" t="n">
-        <v>0</v>
+        <v>21.16</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>451</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>16</v>
       </c>
       <c r="AF33" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG33" t="n">
-        <v>368</v>
+        <v>467</v>
       </c>
       <c r="AH33" t="n">
-        <v>16.24</v>
+        <v>7.83</v>
       </c>
     </row>
     <row r="34">
@@ -4064,106 +4064,106 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>team1789</t>
+          <t>team0980</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>魏胜新</t>
+          <t>朱致远</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>19.97</v>
-      </c>
-      <c r="E34" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="1" t="n">
-        <v>1819</v>
-      </c>
-      <c r="G34" s="1" t="n">
-        <v>-0</v>
-      </c>
-      <c r="H34" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" s="1" t="n">
-        <v>1870</v>
-      </c>
-      <c r="J34" s="1" t="n">
-        <v>-0</v>
-      </c>
-      <c r="K34" t="n">
+        <v>20.06</v>
+      </c>
+      <c r="E34" t="n">
+        <v>4</v>
+      </c>
+      <c r="F34" t="n">
+        <v>557</v>
+      </c>
+      <c r="G34" t="n">
+        <v>23.95</v>
+      </c>
+      <c r="H34" t="n">
+        <v>4</v>
+      </c>
+      <c r="I34" t="n">
+        <v>808</v>
+      </c>
+      <c r="J34" t="n">
+        <v>17.83</v>
+      </c>
+      <c r="K34" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="L34" t="n">
-        <v>726</v>
-      </c>
-      <c r="M34" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="N34" s="1" t="n">
-        <v>2</v>
-      </c>
       <c r="O34" s="1" t="n">
-        <v>1030</v>
+        <v>724</v>
       </c>
       <c r="P34" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q34" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="R34" s="1" t="n">
-        <v>907</v>
-      </c>
-      <c r="S34" s="1" t="n">
-        <v>0</v>
+        <v>11.07</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>5</v>
+      </c>
+      <c r="R34" t="n">
+        <v>307</v>
+      </c>
+      <c r="S34" t="n">
+        <v>36.6</v>
       </c>
       <c r="T34" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U34" t="n">
-        <v>399</v>
+        <v>702</v>
       </c>
       <c r="V34" t="n">
-        <v>27.92</v>
-      </c>
-      <c r="W34" t="n">
-        <v>4</v>
-      </c>
-      <c r="X34" t="n">
-        <v>379</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>19.18</v>
+        <v>11.9</v>
+      </c>
+      <c r="W34" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="X34" s="1" t="n">
+        <v>629</v>
+      </c>
+      <c r="Y34" s="1" t="n">
+        <v>10.84</v>
       </c>
       <c r="Z34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AA34" t="n">
-        <v>200</v>
+        <v>635</v>
       </c>
       <c r="AB34" t="n">
-        <v>37.56</v>
+        <v>13.07</v>
       </c>
       <c r="AC34" t="n">
         <v>3</v>
       </c>
       <c r="AD34" t="n">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="AE34" t="n">
-        <v>14.2</v>
+        <v>13.85</v>
       </c>
       <c r="AF34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AG34" t="n">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="AH34" t="n">
-        <v>17.81</v>
+        <v>23.24</v>
       </c>
     </row>
     <row r="35">
@@ -4172,106 +4172,106 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>team1794</t>
+          <t>team1788</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>成伟业</t>
+          <t>王义轩</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>17.21</v>
-      </c>
-      <c r="E35" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" s="1" t="n">
-        <v>0</v>
+        <v>18.74</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1818</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-0</v>
       </c>
       <c r="H35" s="1" t="n">
         <v>0</v>
       </c>
       <c r="I35" s="1" t="n">
-        <v>0</v>
+        <v>1869</v>
       </c>
       <c r="J35" s="1" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K35" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L35" t="n">
-        <v>303</v>
+        <v>878</v>
       </c>
       <c r="M35" t="n">
-        <v>34.58</v>
+        <v>5.78</v>
       </c>
       <c r="N35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O35" t="n">
-        <v>546</v>
+        <v>387</v>
       </c>
       <c r="P35" t="n">
-        <v>9.56</v>
+        <v>26.53</v>
       </c>
       <c r="Q35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R35" t="n">
-        <v>627</v>
+        <v>366</v>
       </c>
       <c r="S35" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="T35" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="W35" t="n">
-        <v>3</v>
-      </c>
-      <c r="X35" t="n">
-        <v>595</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>7.02</v>
+        <v>34.02</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>847</v>
+      </c>
+      <c r="V35" t="n">
+        <v>4.97</v>
+      </c>
+      <c r="W35" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="Z35" s="1" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA35" s="1" t="n">
-        <v>742</v>
+        <v>0</v>
       </c>
       <c r="AB35" s="1" t="n">
-        <v>2.77</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
         <v>4</v>
       </c>
       <c r="AD35" t="n">
-        <v>382</v>
+        <v>219</v>
       </c>
       <c r="AE35" t="n">
-        <v>26.19</v>
-      </c>
-      <c r="AF35" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG35" s="1" t="n">
-        <v>665</v>
-      </c>
-      <c r="AH35" s="1" t="n">
-        <v>3.4</v>
+        <v>36.11</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>312</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>23.76</v>
       </c>
     </row>
     <row r="36">
@@ -4280,106 +4280,106 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>team0980</t>
+          <t>team0023</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>朱致远</t>
+          <t>刘林果</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>14.16</v>
-      </c>
-      <c r="E36" t="n">
+        <v>17.68</v>
+      </c>
+      <c r="E36" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F36" s="1" t="n">
+        <v>1323</v>
+      </c>
+      <c r="G36" s="1" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="H36" t="n">
         <v>4</v>
       </c>
-      <c r="F36" t="n">
-        <v>557</v>
-      </c>
-      <c r="G36" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="H36" s="1" t="n">
+      <c r="I36" t="n">
+        <v>817</v>
+      </c>
+      <c r="J36" t="n">
+        <v>17.58</v>
+      </c>
+      <c r="K36" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L36" s="1" t="n">
+        <v>926</v>
+      </c>
+      <c r="M36" s="1" t="n">
+        <v>4.88</v>
+      </c>
+      <c r="N36" t="n">
+        <v>3</v>
+      </c>
+      <c r="O36" t="n">
+        <v>718</v>
+      </c>
+      <c r="P36" t="n">
+        <v>11.23</v>
+      </c>
+      <c r="Q36" t="n">
         <v>4</v>
       </c>
-      <c r="I36" s="1" t="n">
-        <v>808</v>
-      </c>
-      <c r="J36" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="O36" s="1" t="n">
-        <v>724</v>
-      </c>
-      <c r="P36" s="1" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>5</v>
-      </c>
       <c r="R36" t="n">
-        <v>307</v>
+        <v>598</v>
       </c>
       <c r="S36" t="n">
-        <v>30.88</v>
+        <v>19.09</v>
       </c>
       <c r="T36" t="n">
         <v>3</v>
       </c>
       <c r="U36" t="n">
-        <v>702</v>
+        <v>653</v>
       </c>
       <c r="V36" t="n">
-        <v>4.12</v>
+        <v>13.39</v>
       </c>
       <c r="W36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="X36" t="n">
-        <v>629</v>
+        <v>388</v>
       </c>
       <c r="Y36" t="n">
-        <v>5.86</v>
+        <v>22.86</v>
       </c>
       <c r="Z36" t="n">
         <v>3</v>
       </c>
       <c r="AA36" t="n">
-        <v>635</v>
+        <v>331</v>
       </c>
       <c r="AB36" t="n">
-        <v>7.78</v>
+        <v>24.78</v>
       </c>
       <c r="AC36" t="n">
         <v>3</v>
       </c>
       <c r="AD36" t="n">
-        <v>496</v>
+        <v>476</v>
       </c>
       <c r="AE36" t="n">
-        <v>14.3</v>
-      </c>
-      <c r="AF36" t="n">
-        <v>4</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>322</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>23.95</v>
+        <v>14.81</v>
+      </c>
+      <c r="AF36" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG36" s="1" t="n">
+        <v>559</v>
+      </c>
+      <c r="AH36" s="1" t="n">
+        <v>5.43</v>
       </c>
     </row>
     <row r="37">
@@ -4388,106 +4388,106 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>team0968</t>
+          <t>team1796</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>李健</t>
+          <t>李梓安</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.58</v>
-      </c>
-      <c r="E37" t="n">
-        <v>5</v>
-      </c>
-      <c r="F37" t="n">
-        <v>482</v>
-      </c>
-      <c r="G37" t="n">
-        <v>19.94</v>
-      </c>
-      <c r="H37" t="n">
-        <v>5</v>
-      </c>
-      <c r="I37" t="n">
-        <v>490</v>
-      </c>
-      <c r="J37" t="n">
-        <v>19.44</v>
-      </c>
-      <c r="K37" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="L37" s="1" t="n">
-        <v>849</v>
-      </c>
-      <c r="M37" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="O37" s="1" t="n">
-        <v>877</v>
-      </c>
-      <c r="P37" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>4</v>
-      </c>
-      <c r="R37" t="n">
-        <v>622</v>
-      </c>
-      <c r="S37" t="n">
-        <v>8.949999999999999</v>
+        <v>12.21</v>
+      </c>
+      <c r="E37" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J37" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" t="n">
+        <v>3</v>
+      </c>
+      <c r="L37" t="n">
+        <v>692</v>
+      </c>
+      <c r="M37" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="N37" t="n">
+        <v>3</v>
+      </c>
+      <c r="O37" t="n">
+        <v>582</v>
+      </c>
+      <c r="P37" t="n">
+        <v>14.79</v>
+      </c>
+      <c r="Q37" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="R37" s="1" t="n">
+        <v>791</v>
+      </c>
+      <c r="S37" s="1" t="n">
+        <v>9.25</v>
       </c>
       <c r="T37" t="n">
         <v>3</v>
       </c>
       <c r="U37" t="n">
-        <v>696</v>
+        <v>775</v>
       </c>
       <c r="V37" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="W37" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="X37" s="1" t="n">
-        <v>1468</v>
-      </c>
-      <c r="Y37" s="1" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Z37" t="n">
+        <v>9.66</v>
+      </c>
+      <c r="W37" t="n">
         <v>3</v>
       </c>
-      <c r="AA37" t="n">
-        <v>425</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>17.62</v>
+      <c r="X37" t="n">
+        <v>639</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>10.57</v>
+      </c>
+      <c r="Z37" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
         <v>3</v>
       </c>
       <c r="AD37" t="n">
-        <v>451</v>
+        <v>532</v>
       </c>
       <c r="AE37" t="n">
-        <v>16.41</v>
-      </c>
-      <c r="AF37" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>467</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>8.35</v>
+        <v>12.13</v>
+      </c>
+      <c r="AF37" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH37" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -4505,25 +4505,25 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="E38" s="1" t="n">
+        <v>9.42</v>
+      </c>
+      <c r="E38" t="n">
         <v>3</v>
       </c>
-      <c r="F38" s="1" t="n">
+      <c r="F38" t="n">
         <v>932</v>
       </c>
-      <c r="G38" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" s="1" t="n">
+      <c r="G38" t="n">
+        <v>9.85</v>
+      </c>
+      <c r="H38" t="n">
         <v>3</v>
       </c>
-      <c r="I38" s="1" t="n">
+      <c r="I38" t="n">
         <v>1159</v>
       </c>
-      <c r="J38" s="1" t="n">
-        <v>0</v>
+      <c r="J38" t="n">
+        <v>6.14</v>
       </c>
       <c r="K38" s="1" t="n">
         <v>2</v>
@@ -4532,16 +4532,16 @@
         <v>892</v>
       </c>
       <c r="M38" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" s="1" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="N38" t="n">
         <v>3</v>
       </c>
-      <c r="O38" s="1" t="n">
+      <c r="O38" t="n">
         <v>817</v>
       </c>
-      <c r="P38" s="1" t="n">
-        <v>0</v>
+      <c r="P38" t="n">
+        <v>8.640000000000001</v>
       </c>
       <c r="Q38" s="1" t="n">
         <v>0</v>
@@ -4552,14 +4552,14 @@
       <c r="S38" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="T38" s="1" t="n">
+      <c r="T38" t="n">
         <v>3</v>
       </c>
-      <c r="U38" s="1" t="n">
+      <c r="U38" t="n">
         <v>803</v>
       </c>
-      <c r="V38" s="1" t="n">
-        <v>0</v>
+      <c r="V38" t="n">
+        <v>8.81</v>
       </c>
       <c r="W38" t="n">
         <v>3</v>
@@ -4568,7 +4568,7 @@
         <v>635</v>
       </c>
       <c r="Y38" t="n">
-        <v>5.66</v>
+        <v>10.68</v>
       </c>
       <c r="Z38" t="n">
         <v>3</v>
@@ -4577,16 +4577,16 @@
         <v>766</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AC38" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="AC38" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="AD38" t="n">
+      <c r="AD38" s="1" t="n">
         <v>674</v>
       </c>
-      <c r="AE38" t="n">
-        <v>3.97</v>
+      <c r="AE38" s="1" t="n">
+        <v>3.57</v>
       </c>
       <c r="AF38" t="n">
         <v>3</v>
@@ -4595,7 +4595,7 @@
         <v>414</v>
       </c>
       <c r="AH38" t="n">
-        <v>14.51</v>
+        <v>13.83</v>
       </c>
     </row>
     <row r="39">
@@ -4604,16 +4604,16 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>team1796</t>
+          <t>team1795</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>李梓安</t>
+          <t>毕梓健</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>6.39</v>
+        <v>7.96</v>
       </c>
       <c r="E39" s="1" t="n">
         <v>0</v>
@@ -4633,68 +4633,68 @@
       <c r="J39" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="K39" t="n">
-        <v>3</v>
-      </c>
-      <c r="L39" t="n">
-        <v>692</v>
-      </c>
-      <c r="M39" t="n">
-        <v>4.54</v>
+      <c r="K39" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L39" s="1" t="n">
+        <v>1120</v>
+      </c>
+      <c r="M39" s="1" t="n">
+        <v>0.62</v>
       </c>
       <c r="N39" t="n">
         <v>3</v>
       </c>
       <c r="O39" t="n">
-        <v>582</v>
+        <v>795</v>
       </c>
       <c r="P39" t="n">
-        <v>8.210000000000001</v>
-      </c>
-      <c r="Q39" s="1" t="n">
+        <v>9.210000000000001</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>2</v>
+      </c>
+      <c r="R39" t="n">
+        <v>927</v>
+      </c>
+      <c r="S39" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="T39" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>2</v>
+      </c>
+      <c r="X39" t="n">
+        <v>832</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="Z39" t="n">
         <v>3</v>
       </c>
-      <c r="R39" s="1" t="n">
-        <v>791</v>
-      </c>
-      <c r="S39" s="1" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="T39" t="n">
-        <v>3</v>
-      </c>
-      <c r="U39" t="n">
-        <v>775</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W39" t="n">
-        <v>3</v>
-      </c>
-      <c r="X39" t="n">
-        <v>639</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>5.52</v>
-      </c>
-      <c r="Z39" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA39" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB39" s="1" t="n">
-        <v>0</v>
+      <c r="AA39" t="n">
+        <v>746</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>8.789999999999999</v>
       </c>
       <c r="AC39" t="n">
         <v>3</v>
       </c>
       <c r="AD39" t="n">
-        <v>532</v>
+        <v>486</v>
       </c>
       <c r="AE39" t="n">
-        <v>12.61</v>
+        <v>14.33</v>
       </c>
       <c r="AF39" s="1" t="n">
         <v>0</v>
@@ -4706,112 +4706,112 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="n">
+    <row r="41">
+      <c r="A41" t="n">
         <v>39</v>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>team1795</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>毕梓健</t>
-        </is>
-      </c>
-      <c r="D40" t="n">
-        <v>5.86</v>
-      </c>
-      <c r="E40" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G40" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L40" s="1" t="n">
-        <v>1120</v>
-      </c>
-      <c r="M40" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" t="n">
-        <v>3</v>
-      </c>
-      <c r="O40" t="n">
-        <v>795</v>
-      </c>
-      <c r="P40" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="Q40" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="R40" s="1" t="n">
-        <v>927</v>
-      </c>
-      <c r="S40" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="T40" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="U40" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="W40" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="X40" s="1" t="n">
-        <v>832</v>
-      </c>
-      <c r="Y40" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>746</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD40" t="n">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>team0979</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>陈卓</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>49</v>
+      </c>
+      <c r="E41" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="F41" s="1" t="n">
+        <v>639</v>
+      </c>
+      <c r="G41" s="1" t="n">
+        <v>21.59</v>
+      </c>
+      <c r="H41" t="n">
+        <v>5</v>
+      </c>
+      <c r="I41" t="n">
         <v>486</v>
       </c>
-      <c r="AE40" t="n">
-        <v>14.77</v>
-      </c>
-      <c r="AF40" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG40" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH40" s="1" t="n">
-        <v>0</v>
+      <c r="J41" t="n">
+        <v>33.34</v>
+      </c>
+      <c r="K41" t="n">
+        <v>4</v>
+      </c>
+      <c r="L41" t="n">
+        <v>371</v>
+      </c>
+      <c r="M41" t="n">
+        <v>30.57</v>
+      </c>
+      <c r="N41" t="n">
+        <v>6</v>
+      </c>
+      <c r="O41" t="n">
+        <v>93</v>
+      </c>
+      <c r="P41" t="n">
+        <v>55.18</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>7</v>
+      </c>
+      <c r="R41" t="n">
+        <v>84</v>
+      </c>
+      <c r="S41" t="n">
+        <v>64.91</v>
+      </c>
+      <c r="T41" t="n">
+        <v>5</v>
+      </c>
+      <c r="U41" t="n">
+        <v>404</v>
+      </c>
+      <c r="V41" t="n">
+        <v>35.02</v>
+      </c>
+      <c r="W41" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" s="1" t="n">
+        <v>1476</v>
+      </c>
+      <c r="Y41" s="1" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z41" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA41" s="1" t="n">
+        <v>1432</v>
+      </c>
+      <c r="AB41" s="1" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>42</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>71.08</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>92</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>52.87</v>
       </c>
     </row>
     <row r="42">
@@ -4829,7 +4829,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>44.63</v>
+        <v>41.22</v>
       </c>
       <c r="E42" t="n">
         <v>6</v>
@@ -4838,7 +4838,7 @@
         <v>172</v>
       </c>
       <c r="G42" t="n">
-        <v>47.17</v>
+        <v>52.6</v>
       </c>
       <c r="H42" t="n">
         <v>6</v>
@@ -4847,7 +4847,7 @@
         <v>212</v>
       </c>
       <c r="J42" t="n">
-        <v>44.17</v>
+        <v>51.3</v>
       </c>
       <c r="K42" t="n">
         <v>7</v>
@@ -4856,15 +4856,15 @@
         <v>39</v>
       </c>
       <c r="M42" t="n">
-        <v>74.08</v>
-      </c>
-      <c r="N42" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" s="1" t="n">
+        <v>75.28</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
         <v>0</v>
       </c>
       <c r="Q42" t="n">
@@ -4874,7 +4874,7 @@
         <v>246</v>
       </c>
       <c r="S42" t="n">
-        <v>34.69</v>
+        <v>39.27</v>
       </c>
       <c r="T42" t="n">
         <v>7</v>
@@ -4883,7 +4883,7 @@
         <v>111</v>
       </c>
       <c r="V42" t="n">
-        <v>67.08</v>
+        <v>69.93000000000001</v>
       </c>
       <c r="W42" s="1" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>753</v>
       </c>
       <c r="AH42" t="n">
-        <v>0.6</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="43">
@@ -4928,106 +4928,106 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>team0979</t>
+          <t>team0993</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>陈卓</t>
+          <t>梁浩然</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>44.47</v>
-      </c>
-      <c r="E43" s="1" t="n">
+        <v>40.19</v>
+      </c>
+      <c r="E43" t="n">
+        <v>5</v>
+      </c>
+      <c r="F43" t="n">
+        <v>240</v>
+      </c>
+      <c r="G43" t="n">
+        <v>41.38</v>
+      </c>
+      <c r="H43" t="n">
+        <v>6</v>
+      </c>
+      <c r="I43" t="n">
+        <v>333</v>
+      </c>
+      <c r="J43" t="n">
+        <v>46.32</v>
+      </c>
+      <c r="K43" t="n">
+        <v>5</v>
+      </c>
+      <c r="L43" t="n">
+        <v>273</v>
+      </c>
+      <c r="M43" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="N43" t="n">
         <v>4</v>
       </c>
-      <c r="F43" s="1" t="n">
-        <v>639</v>
-      </c>
-      <c r="G43" s="1" t="n">
-        <v>8.1</v>
-      </c>
-      <c r="H43" t="n">
-        <v>5</v>
-      </c>
-      <c r="I43" t="n">
-        <v>486</v>
-      </c>
-      <c r="J43" t="n">
-        <v>19.69</v>
-      </c>
-      <c r="K43" t="n">
+      <c r="O43" t="n">
+        <v>423</v>
+      </c>
+      <c r="P43" t="n">
+        <v>25.27</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>5</v>
+      </c>
+      <c r="R43" t="n">
+        <v>396</v>
+      </c>
+      <c r="S43" t="n">
+        <v>32.71</v>
+      </c>
+      <c r="T43" t="n">
+        <v>6</v>
+      </c>
+      <c r="U43" t="n">
+        <v>201</v>
+      </c>
+      <c r="V43" t="n">
+        <v>54.43</v>
+      </c>
+      <c r="W43" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" s="1" t="n">
+        <v>1482</v>
+      </c>
+      <c r="Y43" s="1" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z43" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA43" s="1" t="n">
+        <v>1440</v>
+      </c>
+      <c r="AB43" s="1" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC43" t="n">
         <v>4</v>
       </c>
-      <c r="L43" t="n">
-        <v>371</v>
-      </c>
-      <c r="M43" t="n">
-        <v>23.89</v>
-      </c>
-      <c r="N43" t="n">
-        <v>6</v>
-      </c>
-      <c r="O43" t="n">
-        <v>93</v>
-      </c>
-      <c r="P43" t="n">
-        <v>53.1</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>7</v>
-      </c>
-      <c r="R43" t="n">
-        <v>84</v>
-      </c>
-      <c r="S43" t="n">
-        <v>62.74</v>
-      </c>
-      <c r="T43" t="n">
-        <v>5</v>
-      </c>
-      <c r="U43" t="n">
-        <v>404</v>
-      </c>
-      <c r="V43" t="n">
-        <v>27.57</v>
-      </c>
-      <c r="W43" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="X43" s="1" t="n">
-        <v>1476</v>
-      </c>
-      <c r="Y43" s="1" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Z43" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA43" s="1" t="n">
-        <v>1432</v>
-      </c>
-      <c r="AB43" s="1" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>6</v>
-      </c>
       <c r="AD43" t="n">
-        <v>42</v>
+        <v>183</v>
       </c>
       <c r="AE43" t="n">
-        <v>71.16</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>6</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>92</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>53.17</v>
+        <v>38.41</v>
+      </c>
+      <c r="AF43" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG43" s="1" t="n">
+        <v>1331</v>
+      </c>
+      <c r="AH43" s="1" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="44">
@@ -5036,106 +5036,106 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>team1050</t>
+          <t>team1003</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>侯尔为</t>
+          <t>张鲁豫</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>44</v>
+        <v>39.25</v>
       </c>
       <c r="E44" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F44" t="n">
-        <v>205</v>
+        <v>67</v>
       </c>
       <c r="G44" t="n">
-        <v>37.25</v>
+        <v>66.67</v>
       </c>
       <c r="H44" t="n">
+        <v>6</v>
+      </c>
+      <c r="I44" t="n">
+        <v>309</v>
+      </c>
+      <c r="J44" t="n">
+        <v>47.31</v>
+      </c>
+      <c r="K44" t="n">
+        <v>4</v>
+      </c>
+      <c r="L44" t="n">
+        <v>420</v>
+      </c>
+      <c r="M44" t="n">
+        <v>28.73</v>
+      </c>
+      <c r="N44" t="n">
         <v>7</v>
       </c>
-      <c r="I44" t="n">
-        <v>97</v>
-      </c>
-      <c r="J44" t="n">
-        <v>61.6</v>
-      </c>
-      <c r="K44" t="n">
-        <v>5</v>
-      </c>
-      <c r="L44" t="n">
-        <v>181</v>
-      </c>
-      <c r="M44" t="n">
-        <v>43.06</v>
-      </c>
-      <c r="N44" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="O44" s="1" t="n">
-        <v>1060</v>
-      </c>
-      <c r="P44" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" s="1" t="n">
+      <c r="O44" t="n">
+        <v>50</v>
+      </c>
+      <c r="P44" t="n">
+        <v>67.01000000000001</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>6</v>
+      </c>
+      <c r="R44" t="n">
+        <v>92</v>
+      </c>
+      <c r="S44" t="n">
+        <v>55.22</v>
+      </c>
+      <c r="T44" t="n">
         <v>3</v>
       </c>
-      <c r="R44" s="1" t="n">
-        <v>879</v>
-      </c>
-      <c r="S44" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="U44" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="V44" s="1" t="n">
-        <v>0</v>
+      <c r="U44" t="n">
+        <v>771</v>
+      </c>
+      <c r="V44" t="n">
+        <v>9.789999999999999</v>
       </c>
       <c r="W44" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>201</v>
+        <v>1486</v>
       </c>
       <c r="Y44" t="n">
-        <v>34.09</v>
+        <v>-0</v>
       </c>
       <c r="Z44" s="1" t="n">
         <v>0</v>
       </c>
       <c r="AA44" s="1" t="n">
-        <v>0</v>
+        <v>1445</v>
       </c>
       <c r="AB44" s="1" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC44" s="1" t="n">
         <v>0</v>
       </c>
       <c r="AD44" s="1" t="n">
-        <v>0</v>
+        <v>1380</v>
       </c>
       <c r="AE44" s="1" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF44" s="1" t="n">
         <v>0</v>
       </c>
       <c r="AG44" s="1" t="n">
-        <v>0</v>
+        <v>1335</v>
       </c>
       <c r="AH44" s="1" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="45">
@@ -5144,106 +5144,106 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>team1003</t>
+          <t>team0976</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>张鲁豫</t>
+          <t>蔡佩霖</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>40.4</v>
+        <v>33.14</v>
       </c>
       <c r="E45" t="n">
+        <v>6</v>
+      </c>
+      <c r="F45" t="n">
+        <v>170</v>
+      </c>
+      <c r="G45" t="n">
+        <v>52.68</v>
+      </c>
+      <c r="H45" t="n">
         <v>7</v>
       </c>
-      <c r="F45" t="n">
-        <v>67</v>
-      </c>
-      <c r="G45" t="n">
-        <v>64.22</v>
-      </c>
-      <c r="H45" t="n">
+      <c r="I45" t="n">
+        <v>94</v>
+      </c>
+      <c r="J45" t="n">
+        <v>65.53</v>
+      </c>
+      <c r="K45" t="n">
         <v>6</v>
       </c>
-      <c r="I45" t="n">
-        <v>309</v>
-      </c>
-      <c r="J45" t="n">
-        <v>36.9</v>
-      </c>
-      <c r="K45" t="n">
-        <v>4</v>
-      </c>
       <c r="L45" t="n">
-        <v>420</v>
+        <v>134</v>
       </c>
       <c r="M45" t="n">
-        <v>21.17</v>
+        <v>59.18</v>
       </c>
       <c r="N45" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>65.70999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
+        <v>2</v>
+      </c>
+      <c r="R45" t="n">
+        <v>932</v>
+      </c>
+      <c r="S45" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1490</v>
+      </c>
+      <c r="V45" t="n">
+        <v>-0</v>
+      </c>
+      <c r="W45" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" s="1" t="n">
+        <v>1475</v>
+      </c>
+      <c r="Y45" s="1" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z45" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA45" s="1" t="n">
+        <v>1431</v>
+      </c>
+      <c r="AB45" s="1" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC45" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD45" s="1" t="n">
+        <v>1372</v>
+      </c>
+      <c r="AE45" s="1" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AF45" t="n">
         <v>6</v>
       </c>
-      <c r="R45" t="n">
-        <v>92</v>
-      </c>
-      <c r="S45" t="n">
-        <v>53.17</v>
-      </c>
-      <c r="T45" t="n">
-        <v>3</v>
-      </c>
-      <c r="U45" t="n">
-        <v>771</v>
-      </c>
-      <c r="V45" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W45" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="X45" s="1" t="n">
-        <v>1486</v>
-      </c>
-      <c r="Y45" s="1" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Z45" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA45" s="1" t="n">
-        <v>1445</v>
-      </c>
-      <c r="AB45" s="1" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AC45" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD45" s="1" t="n">
-        <v>1380</v>
-      </c>
-      <c r="AE45" s="1" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AF45" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG45" s="1" t="n">
-        <v>1335</v>
-      </c>
-      <c r="AH45" s="1" t="n">
-        <v>-0</v>
+      <c r="AG45" t="n">
+        <v>117</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>50.91</v>
       </c>
     </row>
     <row r="46">
@@ -5252,88 +5252,88 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>team1005</t>
+          <t>team1006</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>刘永琰</t>
+          <t>徐嘉晨</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>37.61</v>
+        <v>33.12</v>
       </c>
       <c r="E46" t="n">
+        <v>3</v>
+      </c>
+      <c r="F46" t="n">
+        <v>780</v>
+      </c>
+      <c r="G46" t="n">
+        <v>13.14</v>
+      </c>
+      <c r="H46" t="n">
+        <v>4</v>
+      </c>
+      <c r="I46" t="n">
+        <v>674</v>
+      </c>
+      <c r="J46" t="n">
+        <v>21.51</v>
+      </c>
+      <c r="K46" t="n">
+        <v>4</v>
+      </c>
+      <c r="L46" t="n">
+        <v>438</v>
+      </c>
+      <c r="M46" t="n">
+        <v>28.05</v>
+      </c>
+      <c r="N46" t="n">
+        <v>4</v>
+      </c>
+      <c r="O46" t="n">
+        <v>261</v>
+      </c>
+      <c r="P46" t="n">
+        <v>30.92</v>
+      </c>
+      <c r="Q46" t="n">
         <v>7</v>
       </c>
-      <c r="F46" t="n">
-        <v>59</v>
-      </c>
-      <c r="G46" t="n">
-        <v>64.92</v>
-      </c>
-      <c r="H46" t="n">
-        <v>6</v>
-      </c>
-      <c r="I46" t="n">
-        <v>234</v>
-      </c>
-      <c r="J46" t="n">
-        <v>42.52</v>
-      </c>
-      <c r="K46" t="n">
-        <v>3</v>
-      </c>
-      <c r="L46" t="n">
-        <v>672</v>
-      </c>
-      <c r="M46" t="n">
-        <v>5.38</v>
-      </c>
-      <c r="N46" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="U46" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="W46" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="X46" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y46" s="1" t="n">
+      <c r="R46" t="n">
+        <v>40</v>
+      </c>
+      <c r="S46" t="n">
+        <v>67.61</v>
+      </c>
+      <c r="T46" t="n">
+        <v>7</v>
+      </c>
+      <c r="U46" t="n">
+        <v>102</v>
+      </c>
+      <c r="V46" t="n">
+        <v>70.56999999999999</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="n">
         <v>0</v>
       </c>
       <c r="Z46" s="1" t="n">
         <v>0</v>
       </c>
       <c r="AA46" s="1" t="n">
-        <v>1447</v>
+        <v>0</v>
       </c>
       <c r="AB46" s="1" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC46" s="1" t="n">
         <v>0</v>
@@ -5348,7 +5348,7 @@
         <v>0</v>
       </c>
       <c r="AG46" s="1" t="n">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="AH46" s="1" t="n">
         <v>-0</v>
@@ -5360,106 +5360,106 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>team0993</t>
+          <t>team1050</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>梁浩然</t>
+          <t>侯尔为</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>34.24</v>
+        <v>28.62</v>
       </c>
       <c r="E47" t="n">
         <v>5</v>
       </c>
       <c r="F47" t="n">
-        <v>240</v>
+        <v>205</v>
       </c>
       <c r="G47" t="n">
-        <v>35.06</v>
+        <v>42.64</v>
       </c>
       <c r="H47" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I47" t="n">
-        <v>333</v>
+        <v>97</v>
       </c>
       <c r="J47" t="n">
-        <v>35.1</v>
+        <v>65.38</v>
       </c>
       <c r="K47" t="n">
         <v>5</v>
       </c>
       <c r="L47" t="n">
-        <v>273</v>
+        <v>181</v>
       </c>
       <c r="M47" t="n">
-        <v>36.67</v>
+        <v>47.12</v>
       </c>
       <c r="N47" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O47" t="n">
-        <v>423</v>
+        <v>1060</v>
       </c>
       <c r="P47" t="n">
-        <v>18.9</v>
+        <v>1.52</v>
       </c>
       <c r="Q47" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R47" t="n">
-        <v>396</v>
+        <v>879</v>
       </c>
       <c r="S47" t="n">
-        <v>25.31</v>
+        <v>6.94</v>
       </c>
       <c r="T47" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="U47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0</v>
+      </c>
+      <c r="W47" t="n">
+        <v>5</v>
+      </c>
+      <c r="X47" t="n">
         <v>201</v>
       </c>
-      <c r="V47" t="n">
-        <v>50</v>
-      </c>
-      <c r="W47" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="X47" s="1" t="n">
-        <v>1482</v>
-      </c>
-      <c r="Y47" s="1" t="n">
-        <v>-0</v>
+      <c r="Y47" t="n">
+        <v>36.73</v>
       </c>
       <c r="Z47" s="1" t="n">
         <v>0</v>
       </c>
       <c r="AA47" s="1" t="n">
-        <v>1440</v>
+        <v>0</v>
       </c>
       <c r="AB47" s="1" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>4</v>
-      </c>
-      <c r="AD47" t="n">
-        <v>183</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>38.62</v>
+        <v>0</v>
+      </c>
+      <c r="AC47" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD47" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE47" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="AF47" s="1" t="n">
         <v>0</v>
       </c>
       <c r="AG47" s="1" t="n">
-        <v>1331</v>
+        <v>0</v>
       </c>
       <c r="AH47" s="1" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -5477,7 +5477,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>32.87</v>
+        <v>28.21</v>
       </c>
       <c r="E48" t="n">
         <v>5</v>
@@ -5486,7 +5486,7 @@
         <v>302</v>
       </c>
       <c r="G48" t="n">
-        <v>31.19</v>
+        <v>39.14</v>
       </c>
       <c r="H48" t="n">
         <v>6</v>
@@ -5495,7 +5495,7 @@
         <v>272</v>
       </c>
       <c r="J48" t="n">
-        <v>39.67</v>
+        <v>48.83</v>
       </c>
       <c r="K48" t="n">
         <v>5</v>
@@ -5504,7 +5504,7 @@
         <v>231</v>
       </c>
       <c r="M48" t="n">
-        <v>39.58</v>
+        <v>44.77</v>
       </c>
       <c r="N48" t="n">
         <v>4</v>
@@ -5513,7 +5513,7 @@
         <v>337</v>
       </c>
       <c r="P48" t="n">
-        <v>23.2</v>
+        <v>28.27</v>
       </c>
       <c r="Q48" t="n">
         <v>5</v>
@@ -5522,24 +5522,24 @@
         <v>310</v>
       </c>
       <c r="S48" t="n">
-        <v>30.69</v>
-      </c>
-      <c r="T48" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="U48" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="V48" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="W48" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="X48" s="1" t="n">
+        <v>36.47</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" t="n">
         <v>1483</v>
       </c>
-      <c r="Y48" s="1" t="n">
+      <c r="Y48" t="n">
         <v>-0</v>
       </c>
       <c r="Z48" s="1" t="n">
@@ -5576,88 +5576,88 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>team1342</t>
+          <t>team1005</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>张钧睿</t>
+          <t>刘永琰</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>29.19</v>
+        <v>18.85</v>
       </c>
       <c r="E49" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F49" t="n">
-        <v>334</v>
+        <v>59</v>
       </c>
       <c r="G49" t="n">
-        <v>29.19</v>
-      </c>
-      <c r="H49" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="I49" s="1" t="n">
-        <v>903</v>
-      </c>
-      <c r="J49" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="L49" s="1" t="n">
-        <v>823</v>
-      </c>
-      <c r="M49" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q49" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R49" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="S49" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="T49" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="U49" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="V49" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="W49" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="X49" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y49" s="1" t="n">
+        <v>67.06999999999999</v>
+      </c>
+      <c r="H49" t="n">
+        <v>6</v>
+      </c>
+      <c r="I49" t="n">
+        <v>234</v>
+      </c>
+      <c r="J49" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="K49" t="n">
+        <v>3</v>
+      </c>
+      <c r="L49" t="n">
+        <v>672</v>
+      </c>
+      <c r="M49" t="n">
+        <v>14.46</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" t="n">
+        <v>0</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0</v>
+      </c>
+      <c r="X49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y49" t="n">
         <v>0</v>
       </c>
       <c r="Z49" s="1" t="n">
         <v>0</v>
       </c>
       <c r="AA49" s="1" t="n">
-        <v>0</v>
+        <v>1447</v>
       </c>
       <c r="AB49" s="1" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC49" s="1" t="n">
         <v>0</v>
@@ -5672,10 +5672,10 @@
         <v>0</v>
       </c>
       <c r="AG49" s="1" t="n">
-        <v>0</v>
+        <v>1336</v>
       </c>
       <c r="AH49" s="1" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="50">
@@ -5684,106 +5684,106 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>team0974</t>
+          <t>team1797</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>刘永琰</t>
+          <t>林泽洋</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="E50" t="n">
-        <v>5</v>
-      </c>
-      <c r="F50" t="n">
-        <v>393</v>
-      </c>
-      <c r="G50" t="n">
-        <v>25.5</v>
+        <v>15.03</v>
+      </c>
+      <c r="E50" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="H50" s="1" t="n">
         <v>0</v>
       </c>
       <c r="I50" s="1" t="n">
-        <v>1681</v>
+        <v>0</v>
       </c>
       <c r="J50" s="1" t="n">
-        <v>-0</v>
-      </c>
-      <c r="K50" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" s="1" t="n">
-        <v>1523</v>
-      </c>
-      <c r="P50" s="1" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Q50" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" s="1" t="n">
-        <v>1514</v>
-      </c>
-      <c r="S50" s="1" t="n">
-        <v>-0</v>
-      </c>
-      <c r="T50" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="U50" s="1" t="n">
-        <v>1488</v>
-      </c>
-      <c r="V50" s="1" t="n">
-        <v>-0</v>
+        <v>0</v>
+      </c>
+      <c r="K50" t="n">
+        <v>2</v>
+      </c>
+      <c r="L50" t="n">
+        <v>770</v>
+      </c>
+      <c r="M50" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="N50" t="n">
+        <v>3</v>
+      </c>
+      <c r="O50" t="n">
+        <v>828</v>
+      </c>
+      <c r="P50" t="n">
+        <v>8.35</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>4</v>
+      </c>
+      <c r="R50" t="n">
+        <v>641</v>
+      </c>
+      <c r="S50" t="n">
+        <v>17.58</v>
+      </c>
+      <c r="T50" t="n">
+        <v>5</v>
+      </c>
+      <c r="U50" t="n">
+        <v>375</v>
+      </c>
+      <c r="V50" t="n">
+        <v>36.49</v>
       </c>
       <c r="W50" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X50" s="1" t="n">
-        <v>1473</v>
+        <v>1028</v>
       </c>
       <c r="Y50" s="1" t="n">
-        <v>-0</v>
+        <v>0.13</v>
       </c>
       <c r="Z50" s="1" t="n">
         <v>0</v>
       </c>
       <c r="AA50" s="1" t="n">
-        <v>1429</v>
+        <v>0</v>
       </c>
       <c r="AB50" s="1" t="n">
-        <v>-0</v>
-      </c>
-      <c r="AC50" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD50" s="1" t="n">
-        <v>1370</v>
-      </c>
-      <c r="AE50" s="1" t="n">
-        <v>-0</v>
+        <v>0</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>632</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>4.9</v>
       </c>
       <c r="AF50" s="1" t="n">
         <v>0</v>
       </c>
       <c r="AG50" s="1" t="n">
-        <v>1326</v>
+        <v>0</v>
       </c>
       <c r="AH50" s="1" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -5792,16 +5792,16 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>team1797</t>
+          <t>team1793</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>林泽洋</t>
+          <t>常昊天</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>10.93</v>
+        <v>10.15</v>
       </c>
       <c r="E51" s="1" t="n">
         <v>0</v>
@@ -5821,68 +5821,68 @@
       <c r="J51" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="K51" t="n">
+      <c r="K51" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L51" s="1" t="n">
+        <v>1022</v>
+      </c>
+      <c r="M51" s="1" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="N51" t="n">
+        <v>3</v>
+      </c>
+      <c r="O51" t="n">
+        <v>754</v>
+      </c>
+      <c r="P51" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="Q51" t="n">
         <v>2</v>
       </c>
-      <c r="L51" t="n">
-        <v>770</v>
-      </c>
-      <c r="M51" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="N51" s="1" t="n">
+      <c r="R51" t="n">
+        <v>950</v>
+      </c>
+      <c r="S51" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="T51" t="n">
         <v>3</v>
       </c>
-      <c r="O51" s="1" t="n">
-        <v>828</v>
-      </c>
-      <c r="P51" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>4</v>
-      </c>
-      <c r="R51" t="n">
-        <v>641</v>
-      </c>
-      <c r="S51" t="n">
-        <v>8</v>
-      </c>
-      <c r="T51" t="n">
-        <v>5</v>
-      </c>
       <c r="U51" t="n">
-        <v>375</v>
+        <v>776</v>
       </c>
       <c r="V51" t="n">
-        <v>29.58</v>
-      </c>
-      <c r="W51" s="1" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="W51" t="n">
+        <v>3</v>
+      </c>
+      <c r="X51" t="n">
+        <v>628</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>544</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>16.57</v>
+      </c>
+      <c r="AC51" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="X51" s="1" t="n">
-        <v>1028</v>
-      </c>
-      <c r="Y51" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z51" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA51" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB51" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>632</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>5.28</v>
+      <c r="AD51" s="1" t="n">
+        <v>728</v>
+      </c>
+      <c r="AE51" s="1" t="n">
+        <v>0.92</v>
       </c>
       <c r="AF51" s="1" t="n">
         <v>0</v>
@@ -5900,97 +5900,97 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>team1793</t>
+          <t>team1342</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>常昊天</t>
+          <t>张钧睿</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="E52" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="G52" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L52" s="1" t="n">
-        <v>1022</v>
-      </c>
-      <c r="M52" s="1" t="n">
-        <v>0</v>
+        <v>8.57</v>
+      </c>
+      <c r="E52" t="n">
+        <v>5</v>
+      </c>
+      <c r="F52" t="n">
+        <v>334</v>
+      </c>
+      <c r="G52" t="n">
+        <v>37.99</v>
+      </c>
+      <c r="H52" t="n">
+        <v>4</v>
+      </c>
+      <c r="I52" t="n">
+        <v>903</v>
+      </c>
+      <c r="J52" t="n">
+        <v>15.22</v>
+      </c>
+      <c r="K52" t="n">
+        <v>2</v>
+      </c>
+      <c r="L52" t="n">
+        <v>823</v>
+      </c>
+      <c r="M52" t="n">
+        <v>6.81</v>
       </c>
       <c r="N52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>754</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Q52" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="R52" s="1" t="n">
-        <v>950</v>
-      </c>
-      <c r="S52" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
         <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>776</v>
+        <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>628</v>
+        <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="Z52" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>544</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>12.05</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>728</v>
-      </c>
-      <c r="AE52" t="n">
-        <v>1.14</v>
+        <v>0</v>
+      </c>
+      <c r="Z52" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB52" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC52" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD52" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE52" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="AF52" s="1" t="n">
         <v>0</v>
@@ -6017,16 +6017,16 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="E53" s="1" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="E53" t="n">
         <v>1</v>
       </c>
-      <c r="F53" s="1" t="n">
+      <c r="F53" t="n">
         <v>1324</v>
       </c>
-      <c r="G53" s="1" t="n">
-        <v>0</v>
+      <c r="G53" t="n">
+        <v>0.45</v>
       </c>
       <c r="H53" t="n">
         <v>4</v>
@@ -6035,16 +6035,16 @@
         <v>735</v>
       </c>
       <c r="J53" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K53" s="1" t="n">
+        <v>19.84</v>
+      </c>
+      <c r="K53" t="n">
         <v>1</v>
       </c>
-      <c r="L53" s="1" t="n">
+      <c r="L53" t="n">
         <v>995</v>
       </c>
-      <c r="M53" s="1" t="n">
-        <v>0</v>
+      <c r="M53" t="n">
+        <v>1.79</v>
       </c>
       <c r="N53" t="n">
         <v>3</v>
@@ -6053,7 +6053,7 @@
         <v>767</v>
       </c>
       <c r="P53" t="n">
-        <v>1.27</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="Q53" t="n">
         <v>3</v>
@@ -6062,7 +6062,7 @@
         <v>670</v>
       </c>
       <c r="S53" t="n">
-        <v>4.91</v>
+        <v>12.43</v>
       </c>
       <c r="T53" t="n">
         <v>3</v>
@@ -6071,16 +6071,16 @@
         <v>650</v>
       </c>
       <c r="V53" t="n">
-        <v>6.29</v>
-      </c>
-      <c r="W53" s="1" t="n">
+        <v>13.49</v>
+      </c>
+      <c r="W53" t="n">
         <v>1</v>
       </c>
-      <c r="X53" s="1" t="n">
+      <c r="X53" t="n">
         <v>901</v>
       </c>
-      <c r="Y53" s="1" t="n">
-        <v>0</v>
+      <c r="Y53" t="n">
+        <v>1.24</v>
       </c>
       <c r="Z53" s="1" t="n">
         <v>0</v>
@@ -6116,106 +6116,106 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>team1343</t>
+          <t>team0974</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>刘思兰</t>
+          <t>刘永琰</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="E54" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="F54" s="1" t="n">
-        <v>886</v>
-      </c>
-      <c r="G54" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I54" s="1" t="n">
-        <v>1359</v>
-      </c>
-      <c r="J54" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L54" s="1" t="n">
-        <v>1145</v>
-      </c>
-      <c r="M54" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="O54" s="1" t="n">
-        <v>938</v>
-      </c>
-      <c r="P54" s="1" t="n">
-        <v>0</v>
+        <v>5.12</v>
+      </c>
+      <c r="E54" t="n">
+        <v>5</v>
+      </c>
+      <c r="F54" t="n">
+        <v>393</v>
+      </c>
+      <c r="G54" t="n">
+        <v>35.86</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>1681</v>
+      </c>
+      <c r="J54" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
+        <v>1523</v>
+      </c>
+      <c r="P54" t="n">
+        <v>-0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>780</v>
+        <v>1514</v>
       </c>
       <c r="S54" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="T54" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="U54" s="1" t="n">
-        <v>1044</v>
-      </c>
-      <c r="V54" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="W54" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="X54" s="1" t="n">
-        <v>941</v>
-      </c>
-      <c r="Y54" s="1" t="n">
-        <v>0</v>
+        <v>-0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1488</v>
+      </c>
+      <c r="V54" t="n">
+        <v>-0</v>
+      </c>
+      <c r="W54" t="n">
+        <v>0</v>
+      </c>
+      <c r="X54" t="n">
+        <v>1473</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>-0</v>
       </c>
       <c r="Z54" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA54" s="1" t="n">
-        <v>938</v>
+        <v>1429</v>
       </c>
       <c r="AB54" s="1" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC54" s="1" t="n">
         <v>0</v>
       </c>
       <c r="AD54" s="1" t="n">
-        <v>0</v>
+        <v>1370</v>
       </c>
       <c r="AE54" s="1" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF54" s="1" t="n">
         <v>0</v>
       </c>
       <c r="AG54" s="1" t="n">
-        <v>0</v>
+        <v>1326</v>
       </c>
       <c r="AH54" s="1" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="55">
@@ -6233,25 +6233,25 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="E55" s="1" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="E55" t="n">
         <v>3</v>
       </c>
-      <c r="F55" s="1" t="n">
+      <c r="F55" t="n">
         <v>867</v>
       </c>
-      <c r="G55" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" s="1" t="n">
+      <c r="G55" t="n">
+        <v>11.26</v>
+      </c>
+      <c r="H55" t="n">
         <v>4</v>
       </c>
-      <c r="I55" s="1" t="n">
+      <c r="I55" t="n">
         <v>940</v>
       </c>
-      <c r="J55" s="1" t="n">
-        <v>0</v>
+      <c r="J55" t="n">
+        <v>14.2</v>
       </c>
       <c r="K55" t="n">
         <v>2</v>
@@ -6260,42 +6260,42 @@
         <v>779</v>
       </c>
       <c r="M55" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="N55" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="U55" s="1" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" t="n">
         <v>1491</v>
       </c>
-      <c r="V55" s="1" t="n">
-        <v>-0</v>
-      </c>
-      <c r="W55" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="X55" s="1" t="n">
+      <c r="V55" t="n">
+        <v>-0</v>
+      </c>
+      <c r="W55" t="n">
+        <v>0</v>
+      </c>
+      <c r="X55" t="n">
         <v>1480</v>
       </c>
-      <c r="Y55" s="1" t="n">
+      <c r="Y55" t="n">
         <v>-0</v>
       </c>
       <c r="Z55" s="1" t="n">
@@ -6332,106 +6332,106 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>team0104</t>
+          <t>team1343</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>李晨鑫</t>
+          <t>刘思兰</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" s="1" t="n">
-        <v>1428</v>
-      </c>
-      <c r="G56" s="1" t="n">
-        <v>-0</v>
-      </c>
-      <c r="H56" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" s="1" t="n">
-        <v>1502</v>
-      </c>
-      <c r="J56" s="1" t="n">
-        <v>-0</v>
+        <v>3.89</v>
+      </c>
+      <c r="E56" t="n">
+        <v>3</v>
+      </c>
+      <c r="F56" t="n">
+        <v>886</v>
+      </c>
+      <c r="G56" t="n">
+        <v>10.84</v>
+      </c>
+      <c r="H56" t="n">
+        <v>2</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1359</v>
+      </c>
+      <c r="J56" t="n">
+        <v>1.35</v>
       </c>
       <c r="K56" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L56" s="1" t="n">
-        <v>0</v>
+        <v>1145</v>
       </c>
       <c r="M56" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" s="1" t="n">
-        <v>1202</v>
-      </c>
-      <c r="P56" s="1" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Q56" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R56" s="1" t="n">
-        <v>1194</v>
-      </c>
-      <c r="S56" s="1" t="n">
-        <v>-0</v>
-      </c>
-      <c r="T56" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="U56" s="1" t="n">
-        <v>1148</v>
-      </c>
-      <c r="V56" s="1" t="n">
-        <v>-0</v>
-      </c>
-      <c r="W56" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="X56" s="1" t="n">
-        <v>1110</v>
-      </c>
-      <c r="Y56" s="1" t="n">
-        <v>-0</v>
-      </c>
-      <c r="Z56" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA56" s="1" t="n">
-        <v>1041</v>
-      </c>
-      <c r="AB56" s="1" t="n">
-        <v>-0</v>
+        <v>0.38</v>
+      </c>
+      <c r="N56" t="n">
+        <v>2</v>
+      </c>
+      <c r="O56" t="n">
+        <v>938</v>
+      </c>
+      <c r="P56" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>3</v>
+      </c>
+      <c r="R56" t="n">
+        <v>780</v>
+      </c>
+      <c r="S56" t="n">
+        <v>9.539999999999999</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1044</v>
+      </c>
+      <c r="V56" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="W56" t="n">
+        <v>1</v>
+      </c>
+      <c r="X56" t="n">
+        <v>941</v>
+      </c>
+      <c r="Y56" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="Z56" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA56" t="n">
+        <v>938</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>0.46</v>
       </c>
       <c r="AC56" s="1" t="n">
         <v>0</v>
       </c>
       <c r="AD56" s="1" t="n">
-        <v>854</v>
+        <v>0</v>
       </c>
       <c r="AE56" s="1" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF56" s="1" t="n">
         <v>0</v>
       </c>
       <c r="AG56" s="1" t="n">
-        <v>835</v>
+        <v>0</v>
       </c>
       <c r="AH56" s="1" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -6440,103 +6440,103 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>team0975</t>
+          <t>team1049</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>吴语乐天</t>
+          <t>周宇翔</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" s="1" t="n">
-        <v>1585</v>
-      </c>
-      <c r="G57" s="1" t="n">
-        <v>-0</v>
-      </c>
-      <c r="H57" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" s="1" t="n">
-        <v>1682</v>
-      </c>
-      <c r="J57" s="1" t="n">
-        <v>-0</v>
-      </c>
-      <c r="K57" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P57" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q57" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" s="1" t="n">
-        <v>1515</v>
-      </c>
-      <c r="S57" s="1" t="n">
-        <v>-0</v>
-      </c>
-      <c r="T57" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="U57" s="1" t="n">
-        <v>1489</v>
-      </c>
-      <c r="V57" s="1" t="n">
-        <v>-0</v>
-      </c>
-      <c r="W57" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="X57" s="1" t="n">
-        <v>1474</v>
-      </c>
-      <c r="Y57" s="1" t="n">
-        <v>-0</v>
+        <v>1.11</v>
+      </c>
+      <c r="E57" t="n">
+        <v>1</v>
+      </c>
+      <c r="F57" t="n">
+        <v>1308</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H57" t="n">
+        <v>2</v>
+      </c>
+      <c r="I57" t="n">
+        <v>1348</v>
+      </c>
+      <c r="J57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K57" t="n">
+        <v>1</v>
+      </c>
+      <c r="L57" t="n">
+        <v>1098</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="N57" t="n">
+        <v>2</v>
+      </c>
+      <c r="O57" t="n">
+        <v>940</v>
+      </c>
+      <c r="P57" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>1</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1095</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1005</v>
+      </c>
+      <c r="V57" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="W57" t="n">
+        <v>0</v>
+      </c>
+      <c r="X57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y57" t="n">
+        <v>0</v>
       </c>
       <c r="Z57" s="1" t="n">
         <v>0</v>
       </c>
       <c r="AA57" s="1" t="n">
-        <v>1430</v>
+        <v>0</v>
       </c>
       <c r="AB57" s="1" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC57" s="1" t="n">
         <v>0</v>
       </c>
       <c r="AD57" s="1" t="n">
-        <v>1371</v>
+        <v>0</v>
       </c>
       <c r="AE57" s="1" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF57" s="1" t="n">
         <v>0</v>
       </c>
       <c r="AG57" s="1" t="n">
-        <v>1327</v>
+        <v>1366</v>
       </c>
       <c r="AH57" s="1" t="n">
         <v>-0</v>
@@ -6548,85 +6548,85 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>team0996</t>
+          <t>team0104</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>毕皓天</t>
+          <t>李晨鑫</t>
         </is>
       </c>
       <c r="D58" t="n">
         <v>0</v>
       </c>
-      <c r="E58" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" s="1" t="n">
-        <v>1586</v>
-      </c>
-      <c r="G58" s="1" t="n">
-        <v>-0</v>
-      </c>
-      <c r="H58" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" s="1" t="n">
-        <v>1683</v>
-      </c>
-      <c r="J58" s="1" t="n">
-        <v>-0</v>
-      </c>
-      <c r="K58" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="R58" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="S58" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="T58" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="U58" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="V58" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="W58" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="X58" s="1" t="n">
-        <v>1484</v>
-      </c>
-      <c r="Y58" s="1" t="n">
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1428</v>
+      </c>
+      <c r="G58" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>1502</v>
+      </c>
+      <c r="J58" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="n">
+        <v>1202</v>
+      </c>
+      <c r="P58" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
+        <v>1194</v>
+      </c>
+      <c r="S58" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1148</v>
+      </c>
+      <c r="V58" t="n">
+        <v>-0</v>
+      </c>
+      <c r="W58" t="n">
+        <v>0</v>
+      </c>
+      <c r="X58" t="n">
+        <v>1110</v>
+      </c>
+      <c r="Y58" t="n">
         <v>-0</v>
       </c>
       <c r="Z58" s="1" t="n">
         <v>0</v>
       </c>
       <c r="AA58" s="1" t="n">
-        <v>1442</v>
+        <v>1041</v>
       </c>
       <c r="AB58" s="1" t="n">
         <v>-0</v>
@@ -6635,7 +6635,7 @@
         <v>0</v>
       </c>
       <c r="AD58" s="1" t="n">
-        <v>1378</v>
+        <v>854</v>
       </c>
       <c r="AE58" s="1" t="n">
         <v>-0</v>
@@ -6644,7 +6644,7 @@
         <v>0</v>
       </c>
       <c r="AG58" s="1" t="n">
-        <v>1334</v>
+        <v>835</v>
       </c>
       <c r="AH58" s="1" t="n">
         <v>-0</v>
@@ -6656,105 +6656,213 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>team1049</t>
+          <t>team0975</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>周宇翔</t>
+          <t>吴语乐天</t>
         </is>
       </c>
       <c r="D59" t="n">
         <v>0</v>
       </c>
-      <c r="E59" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F59" s="1" t="n">
-        <v>1308</v>
-      </c>
-      <c r="G59" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H59" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I59" s="1" t="n">
-        <v>1348</v>
-      </c>
-      <c r="J59" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L59" s="1" t="n">
-        <v>1098</v>
-      </c>
-      <c r="M59" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="O59" s="1" t="n">
-        <v>940</v>
-      </c>
-      <c r="P59" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q59" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R59" s="1" t="n">
-        <v>1095</v>
-      </c>
-      <c r="S59" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="T59" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="U59" s="1" t="n">
-        <v>1005</v>
-      </c>
-      <c r="V59" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="W59" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="X59" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y59" s="1" t="n">
-        <v>0</v>
+      <c r="E59" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" t="n">
+        <v>1585</v>
+      </c>
+      <c r="G59" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
+        <v>1682</v>
+      </c>
+      <c r="J59" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" t="n">
+        <v>1515</v>
+      </c>
+      <c r="S59" t="n">
+        <v>-0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1489</v>
+      </c>
+      <c r="V59" t="n">
+        <v>-0</v>
+      </c>
+      <c r="W59" t="n">
+        <v>0</v>
+      </c>
+      <c r="X59" t="n">
+        <v>1474</v>
+      </c>
+      <c r="Y59" t="n">
+        <v>-0</v>
       </c>
       <c r="Z59" s="1" t="n">
         <v>0</v>
       </c>
       <c r="AA59" s="1" t="n">
-        <v>0</v>
+        <v>1430</v>
       </c>
       <c r="AB59" s="1" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC59" s="1" t="n">
         <v>0</v>
       </c>
       <c r="AD59" s="1" t="n">
-        <v>0</v>
+        <v>1371</v>
       </c>
       <c r="AE59" s="1" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF59" s="1" t="n">
         <v>0</v>
       </c>
       <c r="AG59" s="1" t="n">
-        <v>1366</v>
+        <v>1327</v>
       </c>
       <c r="AH59" s="1" t="n">
+        <v>-0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>team0996</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>毕皓天</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" t="n">
+        <v>1586</v>
+      </c>
+      <c r="G60" t="n">
+        <v>-0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
+        <v>1683</v>
+      </c>
+      <c r="J60" t="n">
+        <v>-0</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" t="n">
+        <v>0</v>
+      </c>
+      <c r="W60" t="n">
+        <v>0</v>
+      </c>
+      <c r="X60" t="n">
+        <v>1484</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>-0</v>
+      </c>
+      <c r="Z60" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA60" s="1" t="n">
+        <v>1442</v>
+      </c>
+      <c r="AB60" s="1" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AC60" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD60" s="1" t="n">
+        <v>1378</v>
+      </c>
+      <c r="AE60" s="1" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AF60" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG60" s="1" t="n">
+        <v>1334</v>
+      </c>
+      <c r="AH60" s="1" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -6769,7 +6877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -6849,7 +6957,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>82.97</v>
+        <v>84.04000000000001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -6857,7 +6965,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>76.12</v>
+        <v>76.97</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -6865,10 +6973,10 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>71.36</v>
+        <v>72.72</v>
       </c>
       <c r="J2" t="n">
-        <v>76.81999999999999</v>
+        <v>77.91</v>
       </c>
     </row>
     <row r="3">
@@ -6891,7 +6999,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>66.70999999999999</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -6899,7 +7007,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>65.95999999999999</v>
+        <v>67.8</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -6907,10 +7015,10 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>42.88</v>
+        <v>46.41</v>
       </c>
       <c r="J3" t="n">
-        <v>58.52</v>
+        <v>60.81</v>
       </c>
     </row>
     <row r="4">
@@ -6933,7 +7041,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>77.06</v>
+        <v>77.54000000000001</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -6941,7 +7049,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>56.53</v>
+        <v>58.53</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -6949,10 +7057,10 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>33.79</v>
+        <v>40.31</v>
       </c>
       <c r="J4" t="n">
-        <v>55.79</v>
+        <v>58.79</v>
       </c>
     </row>
     <row r="5">
@@ -6975,7 +7083,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53.21</v>
+        <v>56.44</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -6983,7 +7091,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>65.38</v>
+        <v>67.28</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -6991,10 +7099,10 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>38.3</v>
+        <v>41.06</v>
       </c>
       <c r="J5" t="n">
-        <v>52.3</v>
+        <v>54.93</v>
       </c>
     </row>
     <row r="6">
@@ -7017,7 +7125,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>37.16</v>
+        <v>41.47</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -7025,7 +7133,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>61.6</v>
+        <v>62.94</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -7033,10 +7141,10 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>49.51</v>
+        <v>51.86</v>
       </c>
       <c r="J6" t="n">
-        <v>49.42</v>
+        <v>52.09</v>
       </c>
     </row>
     <row r="7">
@@ -7059,7 +7167,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>70.92</v>
+        <v>71.98</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -7067,12 +7175,12 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>21.52</v>
+        <v>26.06</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>46.22</v>
+        <v>49.02</v>
       </c>
     </row>
     <row r="8">
@@ -7095,7 +7203,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>29.42</v>
+        <v>34.39</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -7103,7 +7211,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>38.46</v>
+        <v>43.83</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -7111,10 +7219,10 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>45.21</v>
+        <v>49.28</v>
       </c>
       <c r="J8" t="n">
-        <v>37.7</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="9">
@@ -7123,40 +7231,40 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>三只企鹅</t>
+          <t>疑似mygo</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Gu Gu Ga Ga</t>
+          <t>It's mygo</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>丁培钊</t>
+          <t>罗鑫宇</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>39.97</v>
+        <v>50.37</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>张哲源</t>
+          <t>谢兆轩</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>27.66</v>
+        <v>43.77</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>李子俊</t>
+          <t>朱致远</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>35.08</v>
+        <v>20.06</v>
       </c>
       <c r="J9" t="n">
-        <v>34.24</v>
+        <v>38.07</v>
       </c>
     </row>
     <row r="10">
@@ -7165,40 +7273,40 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>疑似mygo</t>
+          <t>三只企鹅</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>It's mygo</t>
+          <t>Gu Gu Ga Ga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>罗鑫宇</t>
+          <t>丁培钊</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>46.77</v>
+        <v>43.5</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>谢兆轩</t>
+          <t>张哲源</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>38.67</v>
+        <v>32.04</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>朱致远</t>
+          <t>李子俊</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>14.16</v>
+        <v>28.84</v>
       </c>
       <c r="J10" t="n">
-        <v>33.2</v>
+        <v>34.79</v>
       </c>
     </row>
     <row r="11">
@@ -7207,40 +7315,40 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>正着活，反着魔</t>
+          <t>永远别放弃</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>live_evil</t>
+          <t>nevergonnagiveyouup</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>徐嘉晨</t>
+          <t>王义轩</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>31.47</v>
+        <v>18.74</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>蔡佩霖</t>
+          <t>杨鑫</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>54.02</v>
+        <v>33.43</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>李子熙</t>
+          <t>刘芯羽</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>35.95</v>
       </c>
       <c r="J11" t="n">
-        <v>28.5</v>
+        <v>29.37</v>
       </c>
     </row>
     <row r="12">
@@ -7249,40 +7357,40 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>永远别放弃</t>
+          <t>重生之忘带前世记忆打acm</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>nevergonnagiveyouup</t>
+          <t>Re0：acm without memories</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>王义轩</t>
+          <t>成伟业</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>27.18</v>
+        <v>22.53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>杨鑫</t>
+          <t>程博睿</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>27.37</v>
+        <v>49.74</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>刘芯羽</t>
+          <t>李梓安</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>30.31</v>
+        <v>12.21</v>
       </c>
       <c r="J12" t="n">
-        <v>28.29</v>
+        <v>28.16</v>
       </c>
     </row>
     <row r="13">
@@ -7305,7 +7413,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>46.69</v>
+        <v>49.71</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -7313,7 +7421,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>6.45</v>
+        <v>9.42</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -7321,10 +7429,10 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>19.97</v>
+        <v>20.9</v>
       </c>
       <c r="J13" t="n">
-        <v>24.37</v>
+        <v>26.68</v>
       </c>
     </row>
     <row r="14">
@@ -7333,82 +7441,40 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>重生之忘带前世记忆打acm</t>
+          <t>ClosedClaw</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Re0：acm without memories</t>
+          <t>ClosedClaw</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>成伟业</t>
+          <t>毕梓健</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>17.21</v>
+        <v>7.96</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>程博睿</t>
+          <t>李健</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>47.54</v>
+        <v>20.17</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>李梓安</t>
+          <t>刘林果</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>6.39</v>
+        <v>17.68</v>
       </c>
       <c r="J14" t="n">
-        <v>23.71</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>ClosedClaw</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>ClosedClaw</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>毕梓健</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>5.86</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>李健</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>13.58</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>刘林果</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>6.48</v>
+        <v>15.27</v>
       </c>
     </row>
   </sheetData>
